--- a/CNA-Recert-Course/reconciliation/CI_ION_Course_Reconciliation_Master_Tracker.xlsx
+++ b/CNA-Recert-Course/reconciliation/CI_ION_Course_Reconciliation_Master_Tracker.xlsx
@@ -181,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -227,6 +227,48 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -751,336 +793,392 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>CI-ION COURSE RECONCILIATION — MASTER DASHBOARD</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="A2" s="20" t="n"/>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Generated 2026-06-01  •  Export: CI-ION-course-export-...-20260601-114428  •  Status: NOT production-ready — certificate issuance BLOCKED</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Last checked 2026-06-03 - internal reconciliation review may proceed; regulator/survey/certificate submission remains not ready.</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Total tracker rows</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Completed rows</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Blocked rows</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="27" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>P0 blockers</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Needs export verification</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Needs document import</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Blocked - source access/copy errors</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Skipped by copy config</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Needs source repair</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Needs SME review</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Needs compliance review</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Needs legal/CDPH review</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Needs export verification</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Needs app verification</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Needs document import</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Missing documentation count</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Total spreadsheet URLs found</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Copied/imported URL count</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Skipped URL count</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Errored URL count</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Duplicate/anchor URL count</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>57</v>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Still undocumented URL count</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>59</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>External-only URL count</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Folder-not-copied count</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>CNA Recert rows</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>RCFE Admin rows</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Blocked - source access/copy errors</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Case Manager rows</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Cross-Program rows</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Skipped by copy config</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>URL Evidence Breakdown</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>Copied/imported</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Skipped (config)</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Copy/convert errors</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Duplicate/anchor</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>External only</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Folder not copied</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Needs source repair</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Needs SME review</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Needs compliance review</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Needs legal/CDPH review</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Needs app verification</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Missing documentation count</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Total spreadsheet URLs found</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Copied/imported URL count</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Skipped URL count</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Errored URL count</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Duplicate/anchor URL count</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Still undocumented URL count</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>External-only URL count</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Folder-not-copied count</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>CNA Recert rows</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>RCFE Admin rows</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Case Manager rows</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Cross-Program rows</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>URL Evidence Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Copied/imported</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Skipped (config)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Copy/convert errors</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Duplicate/anchor</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>External only</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Folder not copied</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1109,27 +1207,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>App Capability</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>File Evidence</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1401,27 +1499,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Evidence Type</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Source / Record</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1693,27 +1791,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Negative / Acceptance Test</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1994,32 +2092,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Documentation Artifact</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>CNA Recert</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RCFE Admin</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Case Manager</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2828,27 +2926,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Documentation Artifact</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3579,27 +3677,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Documentation Artifact</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4327,12 +4425,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
@@ -4558,112 +4656,112 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>Expected Item</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>Expected Source / Control Doc</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>Actual Export Evidence</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>Actual App Evidence</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>Spreadsheet URL Evidence</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>Gap / Mismatch</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="30" t="inlineStr">
         <is>
           <t>Deliverable To Create</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="P1" s="30" t="inlineStr">
         <is>
           <t>Owner Role</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="Q1" s="30" t="inlineStr">
         <is>
           <t>Reviewer Role</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="30" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="30" t="inlineStr">
         <is>
           <t>Verification Command or File Path</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="T1" s="30" t="inlineStr">
         <is>
           <t>Date Opened</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="U1" s="30" t="inlineStr">
         <is>
           <t>Date Updated</t>
         </is>
       </c>
-      <c r="V1" s="12" t="inlineStr">
+      <c r="V1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4772,7 +4870,7 @@
       </c>
       <c r="U2" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V2" s="13" t="inlineStr">
@@ -4884,7 +4982,7 @@
       </c>
       <c r="U3" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V3" s="14" t="inlineStr">
@@ -4996,7 +5094,7 @@
       </c>
       <c r="U4" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V4" s="13" t="inlineStr">
@@ -5053,7 +5151,7 @@
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>162 URLs classified: 39 copied, 36 skipped, 22 copy/convert errors, 57 duplicate/anchor, 7 external, 1 folder-not-copied</t>
+          <t>162 URLs recalculated: 39 copied, 36 skipped, 22 errored, 57 duplicate/tab-anchor, 7 external-only, 1 owner-decision folder</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
@@ -5063,7 +5161,7 @@
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>59 URLs still need document import/extraction</t>
+          <t>59 still undocumented</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -5108,7 +5206,7 @@
       </c>
       <c r="U5" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V5" s="14" t="inlineStr">
@@ -5220,7 +5318,7 @@
       </c>
       <c r="U6" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V6" s="13" t="inlineStr">
@@ -5332,7 +5430,7 @@
       </c>
       <c r="U7" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V7" s="14" t="inlineStr">
@@ -5444,7 +5542,7 @@
       </c>
       <c r="U8" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V8" s="13" t="inlineStr">
@@ -5556,7 +5654,7 @@
       </c>
       <c r="U9" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V9" s="14" t="inlineStr">
@@ -5668,7 +5766,7 @@
       </c>
       <c r="U10" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V10" s="13" t="inlineStr">
@@ -5780,7 +5878,7 @@
       </c>
       <c r="U11" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V11" s="14" t="inlineStr">
@@ -5892,7 +5990,7 @@
       </c>
       <c r="U12" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V12" s="13" t="inlineStr">
@@ -6004,7 +6102,7 @@
       </c>
       <c r="U13" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V13" s="14" t="inlineStr">
@@ -6116,7 +6214,7 @@
       </c>
       <c r="U14" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V14" s="13" t="inlineStr">
@@ -6228,7 +6326,7 @@
       </c>
       <c r="U15" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V15" s="14" t="inlineStr">
@@ -6340,7 +6438,7 @@
       </c>
       <c r="U16" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V16" s="13" t="inlineStr">
@@ -6452,7 +6550,7 @@
       </c>
       <c r="U17" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V17" s="14" t="inlineStr">
@@ -6564,7 +6662,7 @@
       </c>
       <c r="U18" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V18" s="13" t="inlineStr">
@@ -6676,7 +6774,7 @@
       </c>
       <c r="U19" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V19" s="14" t="inlineStr"/>
@@ -6784,7 +6882,7 @@
       </c>
       <c r="U20" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V20" s="13" t="inlineStr">
@@ -6896,7 +6994,7 @@
       </c>
       <c r="U21" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V21" s="14" t="inlineStr">
@@ -7008,7 +7106,7 @@
       </c>
       <c r="U22" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V22" s="13" t="inlineStr">
@@ -7120,7 +7218,7 @@
       </c>
       <c r="U23" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V23" s="14" t="inlineStr">
@@ -7232,7 +7330,7 @@
       </c>
       <c r="U24" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V24" s="13" t="inlineStr"/>
@@ -7340,7 +7438,7 @@
       </c>
       <c r="U25" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V25" s="14" t="inlineStr">
@@ -7452,7 +7550,7 @@
       </c>
       <c r="U26" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V26" s="13" t="inlineStr"/>
@@ -7560,7 +7658,7 @@
       </c>
       <c r="U27" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V27" s="14" t="inlineStr"/>
@@ -7668,7 +7766,7 @@
       </c>
       <c r="U28" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V28" s="13" t="inlineStr">
@@ -7780,7 +7878,7 @@
       </c>
       <c r="U29" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V29" s="14" t="inlineStr"/>
@@ -7888,7 +7986,7 @@
       </c>
       <c r="U30" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V30" s="13" t="inlineStr">
@@ -8000,7 +8098,7 @@
       </c>
       <c r="U31" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V31" s="14" t="inlineStr">
@@ -8112,7 +8210,7 @@
       </c>
       <c r="U32" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V32" s="13" t="inlineStr"/>
@@ -8220,7 +8318,7 @@
       </c>
       <c r="U33" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V33" s="14" t="inlineStr">
@@ -8332,7 +8430,7 @@
       </c>
       <c r="U34" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V34" s="13" t="inlineStr">
@@ -8444,7 +8542,7 @@
       </c>
       <c r="U35" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V35" s="14" t="inlineStr">
@@ -8556,7 +8654,7 @@
       </c>
       <c r="U36" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V36" s="13" t="inlineStr">
@@ -8668,7 +8766,7 @@
       </c>
       <c r="U37" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V37" s="14" t="inlineStr">
@@ -8780,7 +8878,7 @@
       </c>
       <c r="U38" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V38" s="13" t="inlineStr">
@@ -8892,7 +8990,7 @@
       </c>
       <c r="U39" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V39" s="14" t="inlineStr">
@@ -9004,7 +9102,7 @@
       </c>
       <c r="U40" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V40" s="13" t="inlineStr">
@@ -9093,11 +9191,11 @@
   <dimension ref="A1:W163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -9114,128 +9212,128 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="28" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="34" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>URL Evidence ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Spreadsheet Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Sheet Name</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Row Number</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Cell Address</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Spreadsheet Item / Label</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>URL Type</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>Source Document/File ID</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>Source Tab/Anchor ID</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>Expected Documentation Purpose</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>Copy Status</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>Copied File Name</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>Copied File URL</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="30" t="inlineStr">
         <is>
           <t>Destination Folder</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="P1" s="30" t="inlineStr">
         <is>
           <t>Skipped Reason</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="Q1" s="30" t="inlineStr">
         <is>
           <t>Copy Error</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="30" t="inlineStr">
         <is>
           <t>Equivalent Local/Repo Documentation</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="30" t="inlineStr">
         <is>
           <t>Needs New Documentation?</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="T1" s="30" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="U1" s="30" t="inlineStr">
         <is>
           <t>Owner Role</t>
         </is>
       </c>
-      <c r="V1" s="12" t="inlineStr">
+      <c r="V1" s="30" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="W1" s="12" t="inlineStr">
+      <c r="W1" s="30" t="inlineStr">
         <is>
           <t>Verification Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
           <t>URL-001</t>
@@ -9280,7 +9378,7 @@
       <c r="J2" s="13" t="inlineStr"/>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>Scheduling / booking reference</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
@@ -9301,7 +9399,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U2" s="13" t="inlineStr">
@@ -9316,11 +9414,11 @@
       </c>
       <c r="W2" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=calendar.app.google</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>URL-002</t>
@@ -9365,7 +9463,7 @@
       <c r="J3" s="14" t="inlineStr"/>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>Student/cohort communication channel</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
@@ -9386,7 +9484,7 @@
       </c>
       <c r="T3" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U3" s="14" t="inlineStr">
@@ -9401,11 +9499,11 @@
       </c>
       <c r="W3" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=chat.whatsapp.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>URL-003</t>
@@ -9450,7 +9548,7 @@
       <c r="J4" s="13" t="inlineStr"/>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>External Moodle how-to blog reference</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
@@ -9471,7 +9569,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U4" s="13" t="inlineStr">
@@ -9486,11 +9584,11 @@
       </c>
       <c r="W4" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=discover.trinitydc.edu</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>URL-004</t>
@@ -9543,12 +9641,12 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr"/>
@@ -9568,7 +9666,7 @@
       </c>
       <c r="T5" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U5" s="14" t="inlineStr">
@@ -9583,11 +9681,11 @@
       </c>
       <c r="W5" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>URL-005</t>
@@ -9640,7 +9738,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -9652,11 +9750,7 @@
       <c r="N6" s="13" t="inlineStr"/>
       <c r="O6" s="13" t="inlineStr"/>
       <c r="P6" s="13" t="inlineStr"/>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q6" s="13" t="inlineStr"/>
       <c r="R6" s="13" t="inlineStr"/>
       <c r="S6" s="13" t="inlineStr">
         <is>
@@ -9665,12 +9759,12 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U6" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V6" s="13" t="inlineStr">
@@ -9680,11 +9774,11 @@
       </c>
       <c r="W6" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>URL-006</t>
@@ -9737,7 +9831,7 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
@@ -9749,11 +9843,7 @@
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="14" t="inlineStr"/>
       <c r="P7" s="14" t="inlineStr"/>
-      <c r="Q7" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q7" s="14" t="inlineStr"/>
       <c r="R7" s="14" t="inlineStr"/>
       <c r="S7" s="14" t="inlineStr">
         <is>
@@ -9762,12 +9852,12 @@
       </c>
       <c r="T7" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U7" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V7" s="14" t="inlineStr">
@@ -9777,11 +9867,11 @@
       </c>
       <c r="W7" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>URL-007</t>
@@ -9834,7 +9924,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L8" s="13" t="inlineStr">
@@ -9846,11 +9936,7 @@
       <c r="N8" s="13" t="inlineStr"/>
       <c r="O8" s="13" t="inlineStr"/>
       <c r="P8" s="13" t="inlineStr"/>
-      <c r="Q8" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q8" s="13" t="inlineStr"/>
       <c r="R8" s="13" t="inlineStr"/>
       <c r="S8" s="13" t="inlineStr">
         <is>
@@ -9859,12 +9945,12 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U8" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V8" s="13" t="inlineStr">
@@ -9874,11 +9960,11 @@
       </c>
       <c r="W8" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>URL-008</t>
@@ -9931,7 +10017,7 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
@@ -9943,11 +10029,7 @@
       <c r="N9" s="14" t="inlineStr"/>
       <c r="O9" s="14" t="inlineStr"/>
       <c r="P9" s="14" t="inlineStr"/>
-      <c r="Q9" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q9" s="14" t="inlineStr"/>
       <c r="R9" s="14" t="inlineStr"/>
       <c r="S9" s="14" t="inlineStr">
         <is>
@@ -9956,12 +10038,12 @@
       </c>
       <c r="T9" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U9" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V9" s="14" t="inlineStr">
@@ -9971,11 +10053,11 @@
       </c>
       <c r="W9" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>URL-009</t>
@@ -10028,7 +10110,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
@@ -10040,11 +10122,7 @@
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="13" t="inlineStr"/>
       <c r="P10" s="13" t="inlineStr"/>
-      <c r="Q10" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q10" s="13" t="inlineStr"/>
       <c r="R10" s="13" t="inlineStr"/>
       <c r="S10" s="13" t="inlineStr">
         <is>
@@ -10053,12 +10131,12 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U10" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V10" s="13" t="inlineStr">
@@ -10068,11 +10146,11 @@
       </c>
       <c r="W10" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>URL-010</t>
@@ -10125,7 +10203,7 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
@@ -10137,11 +10215,7 @@
       <c r="N11" s="14" t="inlineStr"/>
       <c r="O11" s="14" t="inlineStr"/>
       <c r="P11" s="14" t="inlineStr"/>
-      <c r="Q11" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q11" s="14" t="inlineStr"/>
       <c r="R11" s="14" t="inlineStr"/>
       <c r="S11" s="14" t="inlineStr">
         <is>
@@ -10150,12 +10224,12 @@
       </c>
       <c r="T11" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U11" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V11" s="14" t="inlineStr">
@@ -10165,11 +10239,11 @@
       </c>
       <c r="W11" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>URL-011</t>
@@ -10222,7 +10296,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
@@ -10234,11 +10308,7 @@
       <c r="N12" s="13" t="inlineStr"/>
       <c r="O12" s="13" t="inlineStr"/>
       <c r="P12" s="13" t="inlineStr"/>
-      <c r="Q12" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q12" s="13" t="inlineStr"/>
       <c r="R12" s="13" t="inlineStr"/>
       <c r="S12" s="13" t="inlineStr">
         <is>
@@ -10247,12 +10317,12 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U12" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V12" s="13" t="inlineStr">
@@ -10262,11 +10332,11 @@
       </c>
       <c r="W12" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>URL-012</t>
@@ -10319,7 +10389,7 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
@@ -10331,11 +10401,7 @@
       <c r="N13" s="14" t="inlineStr"/>
       <c r="O13" s="14" t="inlineStr"/>
       <c r="P13" s="14" t="inlineStr"/>
-      <c r="Q13" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q13" s="14" t="inlineStr"/>
       <c r="R13" s="14" t="inlineStr"/>
       <c r="S13" s="14" t="inlineStr">
         <is>
@@ -10344,12 +10410,12 @@
       </c>
       <c r="T13" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U13" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V13" s="14" t="inlineStr">
@@ -10359,11 +10425,11 @@
       </c>
       <c r="W13" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>URL-013</t>
@@ -10416,7 +10482,7 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -10428,11 +10494,7 @@
       <c r="N14" s="13" t="inlineStr"/>
       <c r="O14" s="13" t="inlineStr"/>
       <c r="P14" s="13" t="inlineStr"/>
-      <c r="Q14" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q14" s="13" t="inlineStr"/>
       <c r="R14" s="13" t="inlineStr"/>
       <c r="S14" s="13" t="inlineStr">
         <is>
@@ -10441,12 +10503,12 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U14" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V14" s="13" t="inlineStr">
@@ -10456,11 +10518,11 @@
       </c>
       <c r="W14" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>URL-014</t>
@@ -10513,7 +10575,7 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-004</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
@@ -10525,11 +10587,7 @@
       <c r="N15" s="14" t="inlineStr"/>
       <c r="O15" s="14" t="inlineStr"/>
       <c r="P15" s="14" t="inlineStr"/>
-      <c r="Q15" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q15" s="14" t="inlineStr"/>
       <c r="R15" s="14" t="inlineStr"/>
       <c r="S15" s="14" t="inlineStr">
         <is>
@@ -10538,12 +10596,12 @@
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V15" s="14" t="inlineStr">
@@ -10553,11 +10611,11 @@
       </c>
       <c r="W15" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
           <t>URL-015</t>
@@ -10606,12 +10664,12 @@
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M16" s="13" t="inlineStr"/>
@@ -10631,7 +10689,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U16" s="13" t="inlineStr">
@@ -10646,11 +10704,11 @@
       </c>
       <c r="W16" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>URL-016</t>
@@ -10699,7 +10757,7 @@
       <c r="J17" s="14" t="inlineStr"/>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>Source document: CI Institute of Nursing Student Catalog 3-17-2026.docx</t>
+          <t>CI Institute of Nursing Student Catalog 3-17-2026.docx</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
@@ -10719,12 +10777,16 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr"/>
       <c r="Q17" s="14" t="inlineStr"/>
-      <c r="R17" s="14" t="inlineStr"/>
+      <c r="R17" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\CI Institute of Nursing Student Catalog 3-17-2026.docx</t>
+        </is>
+      </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -10732,12 +10794,12 @@
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V17" s="14" t="inlineStr">
@@ -10747,11 +10809,11 @@
       </c>
       <c r="W17" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
           <t>URL-017</t>
@@ -10800,12 +10862,12 @@
       <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr"/>
@@ -10825,7 +10887,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U18" s="13" t="inlineStr">
@@ -10840,11 +10902,11 @@
       </c>
       <c r="W18" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
           <t>URL-018</t>
@@ -10897,12 +10959,12 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M19" s="14" t="inlineStr"/>
@@ -10922,7 +10984,7 @@
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -10937,11 +10999,11 @@
       </c>
       <c r="W19" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
           <t>URL-019</t>
@@ -10994,7 +11056,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-018</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
@@ -11006,11 +11068,7 @@
       <c r="N20" s="13" t="inlineStr"/>
       <c r="O20" s="13" t="inlineStr"/>
       <c r="P20" s="13" t="inlineStr"/>
-      <c r="Q20" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q20" s="13" t="inlineStr"/>
       <c r="R20" s="13" t="inlineStr"/>
       <c r="S20" s="13" t="inlineStr">
         <is>
@@ -11019,12 +11077,12 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U20" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V20" s="13" t="inlineStr">
@@ -11034,11 +11092,11 @@
       </c>
       <c r="W20" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
           <t>URL-020</t>
@@ -11091,7 +11149,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-018</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
@@ -11103,11 +11161,7 @@
       <c r="N21" s="14" t="inlineStr"/>
       <c r="O21" s="14" t="inlineStr"/>
       <c r="P21" s="14" t="inlineStr"/>
-      <c r="Q21" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q21" s="14" t="inlineStr"/>
       <c r="R21" s="14" t="inlineStr"/>
       <c r="S21" s="14" t="inlineStr">
         <is>
@@ -11116,12 +11170,12 @@
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V21" s="14" t="inlineStr">
@@ -11131,11 +11185,11 @@
       </c>
       <c r="W21" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
         <is>
           <t>URL-021</t>
@@ -11184,12 +11238,12 @@
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M22" s="13" t="inlineStr"/>
@@ -11209,7 +11263,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U22" s="13" t="inlineStr">
@@ -11224,11 +11278,11 @@
       </c>
       <c r="W22" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
           <t>URL-022</t>
@@ -11277,12 +11331,12 @@
       <c r="J23" s="14" t="inlineStr"/>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M23" s="14" t="inlineStr"/>
@@ -11302,7 +11356,7 @@
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -11317,11 +11371,11 @@
       </c>
       <c r="W23" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
         <is>
           <t>URL-023</t>
@@ -11374,12 +11428,12 @@
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L24" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M24" s="13" t="inlineStr"/>
@@ -11399,7 +11453,7 @@
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U24" s="13" t="inlineStr">
@@ -11414,11 +11468,11 @@
       </c>
       <c r="W24" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>URL-024</t>
@@ -11471,12 +11525,12 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr"/>
@@ -11496,7 +11550,7 @@
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -11511,11 +11565,11 @@
       </c>
       <c r="W25" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>URL-025</t>
@@ -11568,7 +11622,7 @@
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-024</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -11580,11 +11634,7 @@
       <c r="N26" s="13" t="inlineStr"/>
       <c r="O26" s="13" t="inlineStr"/>
       <c r="P26" s="13" t="inlineStr"/>
-      <c r="Q26" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q26" s="13" t="inlineStr"/>
       <c r="R26" s="13" t="inlineStr"/>
       <c r="S26" s="13" t="inlineStr">
         <is>
@@ -11593,12 +11643,12 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U26" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V26" s="13" t="inlineStr">
@@ -11608,11 +11658,11 @@
       </c>
       <c r="W26" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
         <is>
           <t>URL-026</t>
@@ -11665,12 +11715,12 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr"/>
@@ -11690,7 +11740,7 @@
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -11705,11 +11755,11 @@
       </c>
       <c r="W27" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>URL-027</t>
@@ -11762,7 +11812,7 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-026</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
@@ -11774,11 +11824,7 @@
       <c r="N28" s="13" t="inlineStr"/>
       <c r="O28" s="13" t="inlineStr"/>
       <c r="P28" s="13" t="inlineStr"/>
-      <c r="Q28" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q28" s="13" t="inlineStr"/>
       <c r="R28" s="13" t="inlineStr"/>
       <c r="S28" s="13" t="inlineStr">
         <is>
@@ -11787,12 +11833,12 @@
       </c>
       <c r="T28" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U28" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V28" s="13" t="inlineStr">
@@ -11802,11 +11848,11 @@
       </c>
       <c r="W28" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
           <t>URL-028</t>
@@ -11859,12 +11905,12 @@
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr"/>
@@ -11884,7 +11930,7 @@
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -11899,11 +11945,11 @@
       </c>
       <c r="W29" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
           <t>URL-029</t>
@@ -11956,7 +12002,7 @@
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-028</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -11968,11 +12014,7 @@
       <c r="N30" s="13" t="inlineStr"/>
       <c r="O30" s="13" t="inlineStr"/>
       <c r="P30" s="13" t="inlineStr"/>
-      <c r="Q30" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q30" s="13" t="inlineStr"/>
       <c r="R30" s="13" t="inlineStr"/>
       <c r="S30" s="13" t="inlineStr">
         <is>
@@ -11981,12 +12023,12 @@
       </c>
       <c r="T30" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U30" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V30" s="13" t="inlineStr">
@@ -11996,11 +12038,11 @@
       </c>
       <c r="W30" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
           <t>URL-030</t>
@@ -12053,7 +12095,7 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-028</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
@@ -12065,11 +12107,7 @@
       <c r="N31" s="14" t="inlineStr"/>
       <c r="O31" s="14" t="inlineStr"/>
       <c r="P31" s="14" t="inlineStr"/>
-      <c r="Q31" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q31" s="14" t="inlineStr"/>
       <c r="R31" s="14" t="inlineStr"/>
       <c r="S31" s="14" t="inlineStr">
         <is>
@@ -12078,12 +12116,12 @@
       </c>
       <c r="T31" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U31" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V31" s="14" t="inlineStr">
@@ -12093,11 +12131,11 @@
       </c>
       <c r="W31" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
           <t>URL-031</t>
@@ -12146,12 +12184,12 @@
       <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M32" s="13" t="inlineStr"/>
@@ -12171,7 +12209,7 @@
       </c>
       <c r="T32" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U32" s="13" t="inlineStr">
@@ -12186,11 +12224,11 @@
       </c>
       <c r="W32" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>URL-032</t>
@@ -12243,7 +12281,7 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Tutorials - Instructor &amp; Coordinator</t>
+          <t>Tutorials - Instructor &amp; Coordinator</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
@@ -12268,7 +12306,7 @@
       </c>
       <c r="T33" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U33" s="14" t="inlineStr">
@@ -12278,16 +12316,16 @@
       </c>
       <c r="V33" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W33" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
           <t>URL-033</t>
@@ -12340,7 +12378,7 @@
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -12351,11 +12389,7 @@
       <c r="M34" s="13" t="inlineStr"/>
       <c r="N34" s="13" t="inlineStr"/>
       <c r="O34" s="13" t="inlineStr"/>
-      <c r="P34" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P34" s="13" t="inlineStr"/>
       <c r="Q34" s="13" t="inlineStr"/>
       <c r="R34" s="13" t="inlineStr"/>
       <c r="S34" s="13" t="inlineStr">
@@ -12365,12 +12399,12 @@
       </c>
       <c r="T34" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U34" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V34" s="13" t="inlineStr">
@@ -12380,11 +12414,11 @@
       </c>
       <c r="W34" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
         <is>
           <t>URL-034</t>
@@ -12437,7 +12471,7 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
@@ -12448,11 +12482,7 @@
       <c r="M35" s="14" t="inlineStr"/>
       <c r="N35" s="14" t="inlineStr"/>
       <c r="O35" s="14" t="inlineStr"/>
-      <c r="P35" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P35" s="14" t="inlineStr"/>
       <c r="Q35" s="14" t="inlineStr"/>
       <c r="R35" s="14" t="inlineStr"/>
       <c r="S35" s="14" t="inlineStr">
@@ -12462,12 +12492,12 @@
       </c>
       <c r="T35" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U35" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V35" s="14" t="inlineStr">
@@ -12477,11 +12507,11 @@
       </c>
       <c r="W35" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
           <t>URL-035</t>
@@ -12534,7 +12564,7 @@
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
@@ -12545,11 +12575,7 @@
       <c r="M36" s="13" t="inlineStr"/>
       <c r="N36" s="13" t="inlineStr"/>
       <c r="O36" s="13" t="inlineStr"/>
-      <c r="P36" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P36" s="13" t="inlineStr"/>
       <c r="Q36" s="13" t="inlineStr"/>
       <c r="R36" s="13" t="inlineStr"/>
       <c r="S36" s="13" t="inlineStr">
@@ -12559,12 +12585,12 @@
       </c>
       <c r="T36" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U36" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V36" s="13" t="inlineStr">
@@ -12574,11 +12600,11 @@
       </c>
       <c r="W36" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
         <is>
           <t>URL-036</t>
@@ -12631,7 +12657,7 @@
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
@@ -12642,11 +12668,7 @@
       <c r="M37" s="14" t="inlineStr"/>
       <c r="N37" s="14" t="inlineStr"/>
       <c r="O37" s="14" t="inlineStr"/>
-      <c r="P37" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P37" s="14" t="inlineStr"/>
       <c r="Q37" s="14" t="inlineStr"/>
       <c r="R37" s="14" t="inlineStr"/>
       <c r="S37" s="14" t="inlineStr">
@@ -12656,12 +12678,12 @@
       </c>
       <c r="T37" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U37" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V37" s="14" t="inlineStr">
@@ -12671,11 +12693,11 @@
       </c>
       <c r="W37" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
           <t>URL-037</t>
@@ -12728,7 +12750,7 @@
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
@@ -12739,11 +12761,7 @@
       <c r="M38" s="13" t="inlineStr"/>
       <c r="N38" s="13" t="inlineStr"/>
       <c r="O38" s="13" t="inlineStr"/>
-      <c r="P38" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P38" s="13" t="inlineStr"/>
       <c r="Q38" s="13" t="inlineStr"/>
       <c r="R38" s="13" t="inlineStr"/>
       <c r="S38" s="13" t="inlineStr">
@@ -12753,12 +12771,12 @@
       </c>
       <c r="T38" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U38" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V38" s="13" t="inlineStr">
@@ -12768,11 +12786,11 @@
       </c>
       <c r="W38" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
           <t>URL-038</t>
@@ -12825,7 +12843,7 @@
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
@@ -12836,11 +12854,7 @@
       <c r="M39" s="14" t="inlineStr"/>
       <c r="N39" s="14" t="inlineStr"/>
       <c r="O39" s="14" t="inlineStr"/>
-      <c r="P39" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P39" s="14" t="inlineStr"/>
       <c r="Q39" s="14" t="inlineStr"/>
       <c r="R39" s="14" t="inlineStr"/>
       <c r="S39" s="14" t="inlineStr">
@@ -12850,12 +12864,12 @@
       </c>
       <c r="T39" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U39" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V39" s="14" t="inlineStr">
@@ -12865,11 +12879,11 @@
       </c>
       <c r="W39" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
           <t>URL-039</t>
@@ -12922,7 +12936,7 @@
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
@@ -12933,11 +12947,7 @@
       <c r="M40" s="13" t="inlineStr"/>
       <c r="N40" s="13" t="inlineStr"/>
       <c r="O40" s="13" t="inlineStr"/>
-      <c r="P40" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P40" s="13" t="inlineStr"/>
       <c r="Q40" s="13" t="inlineStr"/>
       <c r="R40" s="13" t="inlineStr"/>
       <c r="S40" s="13" t="inlineStr">
@@ -12947,12 +12957,12 @@
       </c>
       <c r="T40" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U40" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V40" s="13" t="inlineStr">
@@ -12962,11 +12972,11 @@
       </c>
       <c r="W40" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
           <t>URL-040</t>
@@ -13019,7 +13029,7 @@
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
@@ -13030,11 +13040,7 @@
       <c r="M41" s="14" t="inlineStr"/>
       <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="14" t="inlineStr"/>
-      <c r="P41" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P41" s="14" t="inlineStr"/>
       <c r="Q41" s="14" t="inlineStr"/>
       <c r="R41" s="14" t="inlineStr"/>
       <c r="S41" s="14" t="inlineStr">
@@ -13044,12 +13050,12 @@
       </c>
       <c r="T41" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U41" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V41" s="14" t="inlineStr">
@@ -13059,11 +13065,11 @@
       </c>
       <c r="W41" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
       <c r="A42" s="13" t="inlineStr">
         <is>
           <t>URL-041</t>
@@ -13116,7 +13122,7 @@
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -13127,11 +13133,7 @@
       <c r="M42" s="13" t="inlineStr"/>
       <c r="N42" s="13" t="inlineStr"/>
       <c r="O42" s="13" t="inlineStr"/>
-      <c r="P42" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P42" s="13" t="inlineStr"/>
       <c r="Q42" s="13" t="inlineStr"/>
       <c r="R42" s="13" t="inlineStr"/>
       <c r="S42" s="13" t="inlineStr">
@@ -13141,12 +13143,12 @@
       </c>
       <c r="T42" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U42" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V42" s="13" t="inlineStr">
@@ -13156,11 +13158,11 @@
       </c>
       <c r="W42" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
           <t>URL-042</t>
@@ -13213,7 +13215,7 @@
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
@@ -13224,11 +13226,7 @@
       <c r="M43" s="14" t="inlineStr"/>
       <c r="N43" s="14" t="inlineStr"/>
       <c r="O43" s="14" t="inlineStr"/>
-      <c r="P43" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P43" s="14" t="inlineStr"/>
       <c r="Q43" s="14" t="inlineStr"/>
       <c r="R43" s="14" t="inlineStr"/>
       <c r="S43" s="14" t="inlineStr">
@@ -13238,12 +13236,12 @@
       </c>
       <c r="T43" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U43" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V43" s="14" t="inlineStr">
@@ -13253,11 +13251,11 @@
       </c>
       <c r="W43" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
           <t>URL-043</t>
@@ -13310,7 +13308,7 @@
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -13321,11 +13319,7 @@
       <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="13" t="inlineStr"/>
       <c r="O44" s="13" t="inlineStr"/>
-      <c r="P44" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P44" s="13" t="inlineStr"/>
       <c r="Q44" s="13" t="inlineStr"/>
       <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="13" t="inlineStr">
@@ -13335,12 +13329,12 @@
       </c>
       <c r="T44" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U44" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V44" s="13" t="inlineStr">
@@ -13350,11 +13344,11 @@
       </c>
       <c r="W44" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
           <t>URL-044</t>
@@ -13407,7 +13401,7 @@
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
@@ -13418,11 +13412,7 @@
       <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="14" t="inlineStr"/>
       <c r="O45" s="14" t="inlineStr"/>
-      <c r="P45" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P45" s="14" t="inlineStr"/>
       <c r="Q45" s="14" t="inlineStr"/>
       <c r="R45" s="14" t="inlineStr"/>
       <c r="S45" s="14" t="inlineStr">
@@ -13432,12 +13422,12 @@
       </c>
       <c r="T45" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U45" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V45" s="14" t="inlineStr">
@@ -13447,11 +13437,11 @@
       </c>
       <c r="W45" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
           <t>URL-045</t>
@@ -13504,7 +13494,7 @@
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -13515,11 +13505,7 @@
       <c r="M46" s="13" t="inlineStr"/>
       <c r="N46" s="13" t="inlineStr"/>
       <c r="O46" s="13" t="inlineStr"/>
-      <c r="P46" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P46" s="13" t="inlineStr"/>
       <c r="Q46" s="13" t="inlineStr"/>
       <c r="R46" s="13" t="inlineStr"/>
       <c r="S46" s="13" t="inlineStr">
@@ -13529,12 +13515,12 @@
       </c>
       <c r="T46" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U46" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V46" s="13" t="inlineStr">
@@ -13544,11 +13530,11 @@
       </c>
       <c r="W46" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
           <t>URL-046</t>
@@ -13601,7 +13587,7 @@
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
@@ -13612,11 +13598,7 @@
       <c r="M47" s="14" t="inlineStr"/>
       <c r="N47" s="14" t="inlineStr"/>
       <c r="O47" s="14" t="inlineStr"/>
-      <c r="P47" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P47" s="14" t="inlineStr"/>
       <c r="Q47" s="14" t="inlineStr"/>
       <c r="R47" s="14" t="inlineStr"/>
       <c r="S47" s="14" t="inlineStr">
@@ -13626,12 +13608,12 @@
       </c>
       <c r="T47" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U47" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V47" s="14" t="inlineStr">
@@ -13641,11 +13623,11 @@
       </c>
       <c r="W47" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
           <t>URL-047</t>
@@ -13698,7 +13680,7 @@
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -13709,11 +13691,7 @@
       <c r="M48" s="13" t="inlineStr"/>
       <c r="N48" s="13" t="inlineStr"/>
       <c r="O48" s="13" t="inlineStr"/>
-      <c r="P48" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P48" s="13" t="inlineStr"/>
       <c r="Q48" s="13" t="inlineStr"/>
       <c r="R48" s="13" t="inlineStr"/>
       <c r="S48" s="13" t="inlineStr">
@@ -13723,12 +13701,12 @@
       </c>
       <c r="T48" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U48" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V48" s="13" t="inlineStr">
@@ -13738,11 +13716,11 @@
       </c>
       <c r="W48" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
           <t>URL-048</t>
@@ -13795,7 +13773,7 @@
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
@@ -13806,11 +13784,7 @@
       <c r="M49" s="14" t="inlineStr"/>
       <c r="N49" s="14" t="inlineStr"/>
       <c r="O49" s="14" t="inlineStr"/>
-      <c r="P49" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P49" s="14" t="inlineStr"/>
       <c r="Q49" s="14" t="inlineStr"/>
       <c r="R49" s="14" t="inlineStr"/>
       <c r="S49" s="14" t="inlineStr">
@@ -13820,12 +13794,12 @@
       </c>
       <c r="T49" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U49" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V49" s="14" t="inlineStr">
@@ -13835,11 +13809,11 @@
       </c>
       <c r="W49" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
           <t>URL-049</t>
@@ -13892,7 +13866,7 @@
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -13903,11 +13877,7 @@
       <c r="M50" s="13" t="inlineStr"/>
       <c r="N50" s="13" t="inlineStr"/>
       <c r="O50" s="13" t="inlineStr"/>
-      <c r="P50" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P50" s="13" t="inlineStr"/>
       <c r="Q50" s="13" t="inlineStr"/>
       <c r="R50" s="13" t="inlineStr"/>
       <c r="S50" s="13" t="inlineStr">
@@ -13917,12 +13887,12 @@
       </c>
       <c r="T50" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U50" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V50" s="13" t="inlineStr">
@@ -13932,11 +13902,11 @@
       </c>
       <c r="W50" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
           <t>URL-050</t>
@@ -13989,7 +13959,7 @@
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
@@ -14000,11 +13970,7 @@
       <c r="M51" s="14" t="inlineStr"/>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="14" t="inlineStr"/>
-      <c r="P51" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P51" s="14" t="inlineStr"/>
       <c r="Q51" s="14" t="inlineStr"/>
       <c r="R51" s="14" t="inlineStr"/>
       <c r="S51" s="14" t="inlineStr">
@@ -14014,12 +13980,12 @@
       </c>
       <c r="T51" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U51" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V51" s="14" t="inlineStr">
@@ -14029,11 +13995,11 @@
       </c>
       <c r="W51" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
       <c r="A52" s="13" t="inlineStr">
         <is>
           <t>URL-051</t>
@@ -14086,7 +14052,7 @@
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -14097,11 +14063,7 @@
       <c r="M52" s="13" t="inlineStr"/>
       <c r="N52" s="13" t="inlineStr"/>
       <c r="O52" s="13" t="inlineStr"/>
-      <c r="P52" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P52" s="13" t="inlineStr"/>
       <c r="Q52" s="13" t="inlineStr"/>
       <c r="R52" s="13" t="inlineStr"/>
       <c r="S52" s="13" t="inlineStr">
@@ -14111,12 +14073,12 @@
       </c>
       <c r="T52" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U52" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V52" s="13" t="inlineStr">
@@ -14126,11 +14088,11 @@
       </c>
       <c r="W52" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
           <t>URL-052</t>
@@ -14183,7 +14145,7 @@
       </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
@@ -14194,11 +14156,7 @@
       <c r="M53" s="14" t="inlineStr"/>
       <c r="N53" s="14" t="inlineStr"/>
       <c r="O53" s="14" t="inlineStr"/>
-      <c r="P53" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P53" s="14" t="inlineStr"/>
       <c r="Q53" s="14" t="inlineStr"/>
       <c r="R53" s="14" t="inlineStr"/>
       <c r="S53" s="14" t="inlineStr">
@@ -14208,12 +14166,12 @@
       </c>
       <c r="T53" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U53" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V53" s="14" t="inlineStr">
@@ -14223,11 +14181,11 @@
       </c>
       <c r="W53" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
       <c r="A54" s="13" t="inlineStr">
         <is>
           <t>URL-053</t>
@@ -14280,7 +14238,7 @@
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -14291,11 +14249,7 @@
       <c r="M54" s="13" t="inlineStr"/>
       <c r="N54" s="13" t="inlineStr"/>
       <c r="O54" s="13" t="inlineStr"/>
-      <c r="P54" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P54" s="13" t="inlineStr"/>
       <c r="Q54" s="13" t="inlineStr"/>
       <c r="R54" s="13" t="inlineStr"/>
       <c r="S54" s="13" t="inlineStr">
@@ -14305,12 +14259,12 @@
       </c>
       <c r="T54" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U54" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V54" s="13" t="inlineStr">
@@ -14320,11 +14274,11 @@
       </c>
       <c r="W54" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
       <c r="A55" s="14" t="inlineStr">
         <is>
           <t>URL-054</t>
@@ -14377,7 +14331,7 @@
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
@@ -14388,11 +14342,7 @@
       <c r="M55" s="14" t="inlineStr"/>
       <c r="N55" s="14" t="inlineStr"/>
       <c r="O55" s="14" t="inlineStr"/>
-      <c r="P55" s="14" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P55" s="14" t="inlineStr"/>
       <c r="Q55" s="14" t="inlineStr"/>
       <c r="R55" s="14" t="inlineStr"/>
       <c r="S55" s="14" t="inlineStr">
@@ -14402,12 +14352,12 @@
       </c>
       <c r="T55" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U55" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V55" s="14" t="inlineStr">
@@ -14417,11 +14367,11 @@
       </c>
       <c r="W55" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
       <c r="A56" s="13" t="inlineStr">
         <is>
           <t>URL-055</t>
@@ -14474,7 +14424,7 @@
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-032</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -14485,11 +14435,7 @@
       <c r="M56" s="13" t="inlineStr"/>
       <c r="N56" s="13" t="inlineStr"/>
       <c r="O56" s="13" t="inlineStr"/>
-      <c r="P56" s="13" t="inlineStr">
-        <is>
-          <t>File exceeds configured max size and was skipped.</t>
-        </is>
-      </c>
+      <c r="P56" s="13" t="inlineStr"/>
       <c r="Q56" s="13" t="inlineStr"/>
       <c r="R56" s="13" t="inlineStr"/>
       <c r="S56" s="13" t="inlineStr">
@@ -14499,12 +14445,12 @@
       </c>
       <c r="T56" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U56" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V56" s="13" t="inlineStr">
@@ -14514,11 +14460,11 @@
       </c>
       <c r="W56" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
         <is>
           <t>URL-056</t>
@@ -14571,12 +14517,12 @@
       </c>
       <c r="K57" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L57" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M57" s="14" t="inlineStr"/>
@@ -14596,7 +14542,7 @@
       </c>
       <c r="T57" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U57" s="14" t="inlineStr">
@@ -14611,11 +14557,11 @@
       </c>
       <c r="W57" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
       <c r="A58" s="13" t="inlineStr">
         <is>
           <t>URL-057</t>
@@ -14668,12 +14614,12 @@
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M58" s="13" t="inlineStr"/>
@@ -14693,7 +14639,7 @@
       </c>
       <c r="T58" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U58" s="13" t="inlineStr">
@@ -14708,11 +14654,11 @@
       </c>
       <c r="W58" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
           <t>URL-058</t>
@@ -14761,7 +14707,7 @@
       <c r="J59" s="14" t="inlineStr"/>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-057</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L59" s="14" t="inlineStr">
@@ -14773,11 +14719,7 @@
       <c r="N59" s="14" t="inlineStr"/>
       <c r="O59" s="14" t="inlineStr"/>
       <c r="P59" s="14" t="inlineStr"/>
-      <c r="Q59" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q59" s="14" t="inlineStr"/>
       <c r="R59" s="14" t="inlineStr"/>
       <c r="S59" s="14" t="inlineStr">
         <is>
@@ -14786,12 +14728,12 @@
       </c>
       <c r="T59" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U59" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V59" s="14" t="inlineStr">
@@ -14801,11 +14743,11 @@
       </c>
       <c r="W59" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
       <c r="A60" s="13" t="inlineStr">
         <is>
           <t>URL-059</t>
@@ -14854,12 +14796,12 @@
       <c r="J60" s="13" t="inlineStr"/>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M60" s="13" t="inlineStr"/>
@@ -14879,7 +14821,7 @@
       </c>
       <c r="T60" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U60" s="13" t="inlineStr">
@@ -14894,11 +14836,11 @@
       </c>
       <c r="W60" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
       <c r="A61" s="14" t="inlineStr">
         <is>
           <t>URL-060</t>
@@ -14951,7 +14893,7 @@
       </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>Source not accessible / not found at export time</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L61" s="14" t="inlineStr">
@@ -14976,7 +14918,7 @@
       </c>
       <c r="T61" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U61" s="14" t="inlineStr">
@@ -14991,11 +14933,11 @@
       </c>
       <c r="W61" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
       <c r="A62" s="13" t="inlineStr">
         <is>
           <t>URL-061</t>
@@ -15044,12 +14986,12 @@
       <c r="J62" s="13" t="inlineStr"/>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr"/>
@@ -15069,7 +15011,7 @@
       </c>
       <c r="T62" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U62" s="13" t="inlineStr">
@@ -15084,11 +15026,11 @@
       </c>
       <c r="W62" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
           <t>URL-062</t>
@@ -15137,12 +15079,12 @@
       <c r="J63" s="14" t="inlineStr"/>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L63" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M63" s="14" t="inlineStr"/>
@@ -15162,7 +15104,7 @@
       </c>
       <c r="T63" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U63" s="14" t="inlineStr">
@@ -15177,11 +15119,11 @@
       </c>
       <c r="W63" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
       <c r="A64" s="13" t="inlineStr">
         <is>
           <t>URL-063</t>
@@ -15234,12 +15176,12 @@
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M64" s="13" t="inlineStr"/>
@@ -15259,7 +15201,7 @@
       </c>
       <c r="T64" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U64" s="13" t="inlineStr">
@@ -15274,11 +15216,11 @@
       </c>
       <c r="W64" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
       <c r="A65" s="14" t="inlineStr">
         <is>
           <t>URL-064</t>
@@ -15331,7 +15273,7 @@
       </c>
       <c r="K65" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-063</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L65" s="14" t="inlineStr">
@@ -15343,11 +15285,7 @@
       <c r="N65" s="14" t="inlineStr"/>
       <c r="O65" s="14" t="inlineStr"/>
       <c r="P65" s="14" t="inlineStr"/>
-      <c r="Q65" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q65" s="14" t="inlineStr"/>
       <c r="R65" s="14" t="inlineStr"/>
       <c r="S65" s="14" t="inlineStr">
         <is>
@@ -15356,12 +15294,12 @@
       </c>
       <c r="T65" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U65" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V65" s="14" t="inlineStr">
@@ -15371,11 +15309,11 @@
       </c>
       <c r="W65" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
       <c r="A66" s="13" t="inlineStr">
         <is>
           <t>URL-065</t>
@@ -15428,7 +15366,7 @@
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-063</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
@@ -15440,11 +15378,7 @@
       <c r="N66" s="13" t="inlineStr"/>
       <c r="O66" s="13" t="inlineStr"/>
       <c r="P66" s="13" t="inlineStr"/>
-      <c r="Q66" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q66" s="13" t="inlineStr"/>
       <c r="R66" s="13" t="inlineStr"/>
       <c r="S66" s="13" t="inlineStr">
         <is>
@@ -15453,12 +15387,12 @@
       </c>
       <c r="T66" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U66" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V66" s="13" t="inlineStr">
@@ -15468,11 +15402,11 @@
       </c>
       <c r="W66" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>URL-066</t>
@@ -15525,7 +15459,7 @@
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-063</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L67" s="14" t="inlineStr">
@@ -15537,11 +15471,7 @@
       <c r="N67" s="14" t="inlineStr"/>
       <c r="O67" s="14" t="inlineStr"/>
       <c r="P67" s="14" t="inlineStr"/>
-      <c r="Q67" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q67" s="14" t="inlineStr"/>
       <c r="R67" s="14" t="inlineStr"/>
       <c r="S67" s="14" t="inlineStr">
         <is>
@@ -15550,12 +15480,12 @@
       </c>
       <c r="T67" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U67" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V67" s="14" t="inlineStr">
@@ -15565,11 +15495,11 @@
       </c>
       <c r="W67" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
       <c r="A68" s="13" t="inlineStr">
         <is>
           <t>URL-067</t>
@@ -15622,12 +15552,12 @@
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L68" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M68" s="13" t="inlineStr"/>
@@ -15647,7 +15577,7 @@
       </c>
       <c r="T68" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U68" s="13" t="inlineStr">
@@ -15662,11 +15592,11 @@
       </c>
       <c r="W68" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>URL-068</t>
@@ -15719,7 +15649,7 @@
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-067</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L69" s="14" t="inlineStr">
@@ -15731,11 +15661,7 @@
       <c r="N69" s="14" t="inlineStr"/>
       <c r="O69" s="14" t="inlineStr"/>
       <c r="P69" s="14" t="inlineStr"/>
-      <c r="Q69" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q69" s="14" t="inlineStr"/>
       <c r="R69" s="14" t="inlineStr"/>
       <c r="S69" s="14" t="inlineStr">
         <is>
@@ -15744,12 +15670,12 @@
       </c>
       <c r="T69" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U69" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V69" s="14" t="inlineStr">
@@ -15759,11 +15685,11 @@
       </c>
       <c r="W69" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
       <c r="A70" s="13" t="inlineStr">
         <is>
           <t>URL-069</t>
@@ -15816,7 +15742,7 @@
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-067</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L70" s="13" t="inlineStr">
@@ -15828,11 +15754,7 @@
       <c r="N70" s="13" t="inlineStr"/>
       <c r="O70" s="13" t="inlineStr"/>
       <c r="P70" s="13" t="inlineStr"/>
-      <c r="Q70" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q70" s="13" t="inlineStr"/>
       <c r="R70" s="13" t="inlineStr"/>
       <c r="S70" s="13" t="inlineStr">
         <is>
@@ -15841,12 +15763,12 @@
       </c>
       <c r="T70" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U70" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V70" s="13" t="inlineStr">
@@ -15856,11 +15778,11 @@
       </c>
       <c r="W70" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>URL-070</t>
@@ -15913,12 +15835,12 @@
       </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L71" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M71" s="14" t="inlineStr"/>
@@ -15938,7 +15860,7 @@
       </c>
       <c r="T71" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U71" s="14" t="inlineStr">
@@ -15953,11 +15875,11 @@
       </c>
       <c r="W71" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
       <c r="A72" s="13" t="inlineStr">
         <is>
           <t>URL-071</t>
@@ -16010,7 +15932,7 @@
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-070</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L72" s="13" t="inlineStr">
@@ -16022,11 +15944,7 @@
       <c r="N72" s="13" t="inlineStr"/>
       <c r="O72" s="13" t="inlineStr"/>
       <c r="P72" s="13" t="inlineStr"/>
-      <c r="Q72" s="13" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q72" s="13" t="inlineStr"/>
       <c r="R72" s="13" t="inlineStr"/>
       <c r="S72" s="13" t="inlineStr">
         <is>
@@ -16035,12 +15953,12 @@
       </c>
       <c r="T72" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U72" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V72" s="13" t="inlineStr">
@@ -16050,11 +15968,11 @@
       </c>
       <c r="W72" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>URL-072</t>
@@ -16107,7 +16025,7 @@
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-070</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L73" s="14" t="inlineStr">
@@ -16119,11 +16037,7 @@
       <c r="N73" s="14" t="inlineStr"/>
       <c r="O73" s="14" t="inlineStr"/>
       <c r="P73" s="14" t="inlineStr"/>
-      <c r="Q73" s="14" t="inlineStr">
-        <is>
-          <t>Converting from application/vnd.google-apps.document to application/vnd.openxmlformats-officedocument.wordprocessingml.document is not supported.</t>
-        </is>
-      </c>
+      <c r="Q73" s="14" t="inlineStr"/>
       <c r="R73" s="14" t="inlineStr"/>
       <c r="S73" s="14" t="inlineStr">
         <is>
@@ -16132,12 +16046,12 @@
       </c>
       <c r="T73" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U73" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V73" s="14" t="inlineStr">
@@ -16147,11 +16061,11 @@
       </c>
       <c r="W73" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
       <c r="A74" s="13" t="inlineStr">
         <is>
           <t>URL-073</t>
@@ -16200,12 +16114,12 @@
       <c r="J74" s="13" t="inlineStr"/>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L74" s="13" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M74" s="13" t="inlineStr"/>
@@ -16225,7 +16139,7 @@
       </c>
       <c r="T74" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U74" s="13" t="inlineStr">
@@ -16240,11 +16154,11 @@
       </c>
       <c r="W74" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>URL-074</t>
@@ -16293,12 +16207,12 @@
       <c r="J75" s="14" t="inlineStr"/>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>Native Google Doc/Sheet could not be converted on export</t>
+          <t>Failed export/copy/convert item from manifest errors[]</t>
         </is>
       </c>
       <c r="L75" s="14" t="inlineStr">
         <is>
-          <t>Copied/imported file exists but needs extraction or conversion</t>
+          <t>Blocked - Source Access / Copy Error</t>
         </is>
       </c>
       <c r="M75" s="14" t="inlineStr"/>
@@ -16318,7 +16232,7 @@
       </c>
       <c r="T75" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U75" s="14" t="inlineStr">
@@ -16333,11 +16247,11 @@
       </c>
       <c r="W75" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
       <c r="A76" s="13" t="inlineStr">
         <is>
           <t>URL-075</t>
@@ -16382,7 +16296,7 @@
       <c r="J76" s="13" t="inlineStr"/>
       <c r="K76" s="13" t="inlineStr">
         <is>
-          <t>Moodle documentation reference (grade hiding)</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L76" s="13" t="inlineStr">
@@ -16403,7 +16317,7 @@
       </c>
       <c r="T76" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U76" s="13" t="inlineStr">
@@ -16418,11 +16332,11 @@
       </c>
       <c r="W76" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=docs.moodle.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
           <t>URL-076</t>
@@ -16471,12 +16385,12 @@
       <c r="J77" s="14" t="inlineStr"/>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>Folder not exported: Admission Exam</t>
+          <t>Folder found but not copied: Admission Exam</t>
         </is>
       </c>
       <c r="L77" s="14" t="inlineStr">
         <is>
-          <t>Folder was found but not copied because folder copying was disabled</t>
+          <t>Needs owner decision</t>
         </is>
       </c>
       <c r="M77" s="14" t="inlineStr"/>
@@ -16496,7 +16410,7 @@
       </c>
       <c r="T77" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U77" s="14" t="inlineStr">
@@ -16511,11 +16425,11 @@
       </c>
       <c r="W77" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
       <c r="A78" s="13" t="inlineStr">
         <is>
           <t>URL-077</t>
@@ -16564,7 +16478,7 @@
       <c r="J78" s="13" t="inlineStr"/>
       <c r="K78" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Taking Quizzes and Exams.mp4</t>
+          <t>Moodle Tutorials - Taking Quizzes and Exams.mp4</t>
         </is>
       </c>
       <c r="L78" s="13" t="inlineStr">
@@ -16589,7 +16503,7 @@
       </c>
       <c r="T78" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U78" s="13" t="inlineStr">
@@ -16599,16 +16513,16 @@
       </c>
       <c r="V78" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W78" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
       <c r="A79" s="14" t="inlineStr">
         <is>
           <t>URL-078</t>
@@ -16657,7 +16571,7 @@
       <c r="J79" s="14" t="inlineStr"/>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-077</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L79" s="14" t="inlineStr">
@@ -16668,11 +16582,7 @@
       <c r="M79" s="14" t="inlineStr"/>
       <c r="N79" s="14" t="inlineStr"/>
       <c r="O79" s="14" t="inlineStr"/>
-      <c r="P79" s="14" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P79" s="14" t="inlineStr"/>
       <c r="Q79" s="14" t="inlineStr"/>
       <c r="R79" s="14" t="inlineStr"/>
       <c r="S79" s="14" t="inlineStr">
@@ -16682,12 +16592,12 @@
       </c>
       <c r="T79" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U79" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V79" s="14" t="inlineStr">
@@ -16697,11 +16607,11 @@
       </c>
       <c r="W79" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
       <c r="A80" s="13" t="inlineStr">
         <is>
           <t>URL-079</t>
@@ -16750,7 +16660,7 @@
       <c r="J80" s="13" t="inlineStr"/>
       <c r="K80" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 17 - Positions on Side</t>
+          <t>CNA Skill 17 - Positions on Side</t>
         </is>
       </c>
       <c r="L80" s="13" t="inlineStr">
@@ -16775,7 +16685,7 @@
       </c>
       <c r="T80" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U80" s="13" t="inlineStr">
@@ -16785,16 +16695,16 @@
       </c>
       <c r="V80" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W80" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
       <c r="A81" s="14" t="inlineStr">
         <is>
           <t>URL-080</t>
@@ -16843,7 +16753,7 @@
       <c r="J81" s="14" t="inlineStr"/>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-16.pdf</t>
         </is>
       </c>
       <c r="L81" s="14" t="inlineStr">
@@ -16863,12 +16773,16 @@
       </c>
       <c r="O81" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P81" s="14" t="inlineStr"/>
       <c r="Q81" s="14" t="inlineStr"/>
-      <c r="R81" s="14" t="inlineStr"/>
+      <c r="R81" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-16.pdf</t>
+        </is>
+      </c>
       <c r="S81" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -16876,12 +16790,12 @@
       </c>
       <c r="T81" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U81" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V81" s="14" t="inlineStr">
@@ -16891,11 +16805,11 @@
       </c>
       <c r="W81" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
       <c r="A82" s="13" t="inlineStr">
         <is>
           <t>URL-081</t>
@@ -16944,7 +16858,7 @@
       <c r="J82" s="13" t="inlineStr"/>
       <c r="K82" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 8 - Donning and Removing PPE</t>
+          <t>CNA Skill 8 - Donning and Removing PPE</t>
         </is>
       </c>
       <c r="L82" s="13" t="inlineStr">
@@ -16969,7 +16883,7 @@
       </c>
       <c r="T82" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U82" s="13" t="inlineStr">
@@ -16979,16 +16893,16 @@
       </c>
       <c r="V82" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W82" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
       <c r="A83" s="14" t="inlineStr">
         <is>
           <t>URL-082</t>
@@ -17037,7 +16951,7 @@
       <c r="J83" s="14" t="inlineStr"/>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>Source document: CI-ION_ Pre-Orientation Student Catalog Test.pdf</t>
+          <t>CI-ION_ Pre-Orientation Student Catalog Test.pdf</t>
         </is>
       </c>
       <c r="L83" s="14" t="inlineStr">
@@ -17057,12 +16971,16 @@
       </c>
       <c r="O83" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P83" s="14" t="inlineStr"/>
       <c r="Q83" s="14" t="inlineStr"/>
-      <c r="R83" s="14" t="inlineStr"/>
+      <c r="R83" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\CI-ION_ Pre-Orientation Student Catalog Test.pdf</t>
+        </is>
+      </c>
       <c r="S83" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -17070,12 +16988,12 @@
       </c>
       <c r="T83" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U83" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V83" s="14" t="inlineStr">
@@ -17085,11 +17003,11 @@
       </c>
       <c r="W83" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
       <c r="A84" s="13" t="inlineStr">
         <is>
           <t>URL-083</t>
@@ -17138,7 +17056,7 @@
       <c r="J84" s="13" t="inlineStr"/>
       <c r="K84" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-12.pdf</t>
         </is>
       </c>
       <c r="L84" s="13" t="inlineStr">
@@ -17158,12 +17076,16 @@
       </c>
       <c r="O84" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P84" s="13" t="inlineStr"/>
       <c r="Q84" s="13" t="inlineStr"/>
-      <c r="R84" s="13" t="inlineStr"/>
+      <c r="R84" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-12.pdf</t>
+        </is>
+      </c>
       <c r="S84" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -17171,12 +17093,12 @@
       </c>
       <c r="T84" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U84" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V84" s="13" t="inlineStr">
@@ -17186,11 +17108,11 @@
       </c>
       <c r="W84" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
       <c r="A85" s="14" t="inlineStr">
         <is>
           <t>URL-084</t>
@@ -17239,7 +17161,7 @@
       <c r="J85" s="14" t="inlineStr"/>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-1.pdf</t>
         </is>
       </c>
       <c r="L85" s="14" t="inlineStr">
@@ -17259,12 +17181,16 @@
       </c>
       <c r="O85" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P85" s="14" t="inlineStr"/>
       <c r="Q85" s="14" t="inlineStr"/>
-      <c r="R85" s="14" t="inlineStr"/>
+      <c r="R85" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-1.pdf</t>
+        </is>
+      </c>
       <c r="S85" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -17272,12 +17198,12 @@
       </c>
       <c r="T85" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U85" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V85" s="14" t="inlineStr">
@@ -17287,11 +17213,11 @@
       </c>
       <c r="W85" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
       <c r="A86" s="13" t="inlineStr">
         <is>
           <t>URL-085</t>
@@ -17340,7 +17266,7 @@
       <c r="J86" s="13" t="inlineStr"/>
       <c r="K86" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 18 - Provides Catheter Care for Female</t>
+          <t>CNA Skill 18 - Provides Catheter Care for Female</t>
         </is>
       </c>
       <c r="L86" s="13" t="inlineStr">
@@ -17365,7 +17291,7 @@
       </c>
       <c r="T86" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U86" s="13" t="inlineStr">
@@ -17375,16 +17301,16 @@
       </c>
       <c r="V86" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W86" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
       <c r="A87" s="14" t="inlineStr">
         <is>
           <t>URL-086</t>
@@ -17433,7 +17359,7 @@
       <c r="J87" s="14" t="inlineStr"/>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Participating in Synchronous Sessions.mp4</t>
+          <t>Moodle Tutorials - Participating in Synchronous Sessions.mp4</t>
         </is>
       </c>
       <c r="L87" s="14" t="inlineStr">
@@ -17458,7 +17384,7 @@
       </c>
       <c r="T87" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U87" s="14" t="inlineStr">
@@ -17468,16 +17394,16 @@
       </c>
       <c r="V87" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W87" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
       <c r="A88" s="13" t="inlineStr">
         <is>
           <t>URL-087</t>
@@ -17526,7 +17452,7 @@
       <c r="J88" s="13" t="inlineStr"/>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-086</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L88" s="13" t="inlineStr">
@@ -17537,11 +17463,7 @@
       <c r="M88" s="13" t="inlineStr"/>
       <c r="N88" s="13" t="inlineStr"/>
       <c r="O88" s="13" t="inlineStr"/>
-      <c r="P88" s="13" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P88" s="13" t="inlineStr"/>
       <c r="Q88" s="13" t="inlineStr"/>
       <c r="R88" s="13" t="inlineStr"/>
       <c r="S88" s="13" t="inlineStr">
@@ -17551,12 +17473,12 @@
       </c>
       <c r="T88" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U88" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V88" s="13" t="inlineStr">
@@ -17566,11 +17488,11 @@
       </c>
       <c r="W88" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
       <c r="A89" s="14" t="inlineStr">
         <is>
           <t>URL-088</t>
@@ -17619,7 +17541,7 @@
       <c r="J89" s="14" t="inlineStr"/>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 15 Module 13 Long Term Patient Resident.pdf</t>
+          <t>PM Day 15 Module 13 Long Term Patient Resident.pdf</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
@@ -17639,12 +17561,16 @@
       </c>
       <c r="O89" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P89" s="14" t="inlineStr"/>
       <c r="Q89" s="14" t="inlineStr"/>
-      <c r="R89" s="14" t="inlineStr"/>
+      <c r="R89" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 15 Module 13 Long Term Patient Resident.pdf</t>
+        </is>
+      </c>
       <c r="S89" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -17652,12 +17578,12 @@
       </c>
       <c r="T89" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U89" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V89" s="14" t="inlineStr">
@@ -17667,11 +17593,11 @@
       </c>
       <c r="W89" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1">
       <c r="A90" s="13" t="inlineStr">
         <is>
           <t>URL-089</t>
@@ -17720,7 +17646,7 @@
       <c r="J90" s="13" t="inlineStr"/>
       <c r="K90" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-3.pdf</t>
         </is>
       </c>
       <c r="L90" s="13" t="inlineStr">
@@ -17740,12 +17666,16 @@
       </c>
       <c r="O90" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P90" s="13" t="inlineStr"/>
       <c r="Q90" s="13" t="inlineStr"/>
-      <c r="R90" s="13" t="inlineStr"/>
+      <c r="R90" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-3.pdf</t>
+        </is>
+      </c>
       <c r="S90" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -17753,12 +17683,12 @@
       </c>
       <c r="T90" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U90" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V90" s="13" t="inlineStr">
@@ -17768,11 +17698,11 @@
       </c>
       <c r="W90" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
       <c r="A91" s="14" t="inlineStr">
         <is>
           <t>URL-090</t>
@@ -17821,7 +17751,7 @@
       <c r="J91" s="14" t="inlineStr"/>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 11 - Gives Modified Bed Bath (Face and One Arm, Hand and Underarm)</t>
+          <t>CNA Skill 11 - Gives Modified Bed Bath (Face and One Arm, Hand and Underarm)</t>
         </is>
       </c>
       <c r="L91" s="14" t="inlineStr">
@@ -17846,7 +17776,7 @@
       </c>
       <c r="T91" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U91" s="14" t="inlineStr">
@@ -17856,16 +17786,16 @@
       </c>
       <c r="V91" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W91" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
       <c r="A92" s="13" t="inlineStr">
         <is>
           <t>URL-091</t>
@@ -17914,7 +17844,7 @@
       <c r="J92" s="13" t="inlineStr"/>
       <c r="K92" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 6 - Counts and Recounts Radial Pulse</t>
+          <t>CNA Skill 6 - Counts and Recounts Radial Pulse</t>
         </is>
       </c>
       <c r="L92" s="13" t="inlineStr">
@@ -17939,7 +17869,7 @@
       </c>
       <c r="T92" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U92" s="13" t="inlineStr">
@@ -17949,16 +17879,16 @@
       </c>
       <c r="V92" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W92" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
       <c r="A93" s="14" t="inlineStr">
         <is>
           <t>URL-092</t>
@@ -18007,7 +17937,7 @@
       <c r="J93" s="14" t="inlineStr"/>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Engaging in Forums.mp4</t>
+          <t>Moodle Tutorials - Engaging in Forums.mp4</t>
         </is>
       </c>
       <c r="L93" s="14" t="inlineStr">
@@ -18032,7 +17962,7 @@
       </c>
       <c r="T93" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U93" s="14" t="inlineStr">
@@ -18042,16 +17972,16 @@
       </c>
       <c r="V93" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W93" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
       <c r="A94" s="13" t="inlineStr">
         <is>
           <t>URL-093</t>
@@ -18100,7 +18030,7 @@
       <c r="J94" s="13" t="inlineStr"/>
       <c r="K94" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-092</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L94" s="13" t="inlineStr">
@@ -18111,11 +18041,7 @@
       <c r="M94" s="13" t="inlineStr"/>
       <c r="N94" s="13" t="inlineStr"/>
       <c r="O94" s="13" t="inlineStr"/>
-      <c r="P94" s="13" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P94" s="13" t="inlineStr"/>
       <c r="Q94" s="13" t="inlineStr"/>
       <c r="R94" s="13" t="inlineStr"/>
       <c r="S94" s="13" t="inlineStr">
@@ -18125,12 +18051,12 @@
       </c>
       <c r="T94" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U94" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V94" s="13" t="inlineStr">
@@ -18140,11 +18066,11 @@
       </c>
       <c r="W94" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
       <c r="A95" s="14" t="inlineStr">
         <is>
           <t>URL-094</t>
@@ -18193,7 +18119,7 @@
       <c r="J95" s="14" t="inlineStr"/>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Navigating Home &amp; Dashboard.mp4</t>
+          <t>Moodle Tutorials - Navigating Home &amp; Dashboard.mp4</t>
         </is>
       </c>
       <c r="L95" s="14" t="inlineStr">
@@ -18218,7 +18144,7 @@
       </c>
       <c r="T95" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U95" s="14" t="inlineStr">
@@ -18228,16 +18154,16 @@
       </c>
       <c r="V95" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W95" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
       <c r="A96" s="13" t="inlineStr">
         <is>
           <t>URL-095</t>
@@ -18286,7 +18212,7 @@
       <c r="J96" s="13" t="inlineStr"/>
       <c r="K96" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-094</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L96" s="13" t="inlineStr">
@@ -18297,11 +18223,7 @@
       <c r="M96" s="13" t="inlineStr"/>
       <c r="N96" s="13" t="inlineStr"/>
       <c r="O96" s="13" t="inlineStr"/>
-      <c r="P96" s="13" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P96" s="13" t="inlineStr"/>
       <c r="Q96" s="13" t="inlineStr"/>
       <c r="R96" s="13" t="inlineStr"/>
       <c r="S96" s="13" t="inlineStr">
@@ -18311,12 +18233,12 @@
       </c>
       <c r="T96" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U96" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V96" s="13" t="inlineStr">
@@ -18326,11 +18248,11 @@
       </c>
       <c r="W96" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
       <c r="A97" s="14" t="inlineStr">
         <is>
           <t>URL-096</t>
@@ -18379,7 +18301,7 @@
       <c r="J97" s="14" t="inlineStr"/>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 19 - Provides Foot Care on One Foot</t>
+          <t>CNA Skill 19 - Provides Foot Care on One Foot</t>
         </is>
       </c>
       <c r="L97" s="14" t="inlineStr">
@@ -18404,7 +18326,7 @@
       </c>
       <c r="T97" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U97" s="14" t="inlineStr">
@@ -18414,16 +18336,16 @@
       </c>
       <c r="V97" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W97" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
       <c r="A98" s="13" t="inlineStr">
         <is>
           <t>URL-097</t>
@@ -18472,7 +18394,7 @@
       <c r="J98" s="13" t="inlineStr"/>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 9 - Dresses Client with Affected Right Arm</t>
+          <t>CNA Skill 9 - Dresses Client with Affected Right Arm</t>
         </is>
       </c>
       <c r="L98" s="13" t="inlineStr">
@@ -18497,7 +18419,7 @@
       </c>
       <c r="T98" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U98" s="13" t="inlineStr">
@@ -18507,16 +18429,16 @@
       </c>
       <c r="V98" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W98" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
       <c r="A99" s="14" t="inlineStr">
         <is>
           <t>URL-098</t>
@@ -18565,7 +18487,7 @@
       <c r="J99" s="14" t="inlineStr"/>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 1 - Hand Hygiene (Hand Washing)</t>
+          <t>CNA Skill 1 - Hand Hygiene (Hand Washing)</t>
         </is>
       </c>
       <c r="L99" s="14" t="inlineStr">
@@ -18590,7 +18512,7 @@
       </c>
       <c r="T99" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U99" s="14" t="inlineStr">
@@ -18600,16 +18522,16 @@
       </c>
       <c r="V99" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W99" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
       <c r="A100" s="13" t="inlineStr">
         <is>
           <t>URL-099</t>
@@ -18658,7 +18580,7 @@
       <c r="J100" s="13" t="inlineStr"/>
       <c r="K100" s="13" t="inlineStr">
         <is>
-          <t>Source document: Cover_Tutorials_Text.png</t>
+          <t>Cover_Tutorials_Text.png</t>
         </is>
       </c>
       <c r="L100" s="13" t="inlineStr">
@@ -18678,12 +18600,16 @@
       </c>
       <c r="O100" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P100" s="13" t="inlineStr"/>
       <c r="Q100" s="13" t="inlineStr"/>
-      <c r="R100" s="13" t="inlineStr"/>
+      <c r="R100" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Cover_Tutorials_Text.png</t>
+        </is>
+      </c>
       <c r="S100" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -18691,12 +18617,12 @@
       </c>
       <c r="T100" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U100" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V100" s="13" t="inlineStr">
@@ -18706,11 +18632,11 @@
       </c>
       <c r="W100" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
       <c r="A101" s="14" t="inlineStr">
         <is>
           <t>URL-100</t>
@@ -18759,7 +18685,7 @@
       <c r="J101" s="14" t="inlineStr"/>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>Source document: Cover_Admission_Text.png</t>
+          <t>Cover_Admission_Text.png</t>
         </is>
       </c>
       <c r="L101" s="14" t="inlineStr">
@@ -18779,12 +18705,16 @@
       </c>
       <c r="O101" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P101" s="14" t="inlineStr"/>
       <c r="Q101" s="14" t="inlineStr"/>
-      <c r="R101" s="14" t="inlineStr"/>
+      <c r="R101" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Cover_Admission_Text.png</t>
+        </is>
+      </c>
       <c r="S101" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -18792,12 +18722,12 @@
       </c>
       <c r="T101" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U101" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V101" s="14" t="inlineStr">
@@ -18807,11 +18737,11 @@
       </c>
       <c r="W101" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
       <c r="A102" s="13" t="inlineStr">
         <is>
           <t>URL-101</t>
@@ -18860,7 +18790,7 @@
       <c r="J102" s="13" t="inlineStr"/>
       <c r="K102" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Accessing Course Content.mp4</t>
+          <t>Moodle Tutorials - Accessing Course Content.mp4</t>
         </is>
       </c>
       <c r="L102" s="13" t="inlineStr">
@@ -18885,7 +18815,7 @@
       </c>
       <c r="T102" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U102" s="13" t="inlineStr">
@@ -18895,16 +18825,16 @@
       </c>
       <c r="V102" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W102" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
       <c r="A103" s="14" t="inlineStr">
         <is>
           <t>URL-102</t>
@@ -18953,7 +18883,7 @@
       <c r="J103" s="14" t="inlineStr"/>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Monitoring Attendance.mp4</t>
+          <t>Moodle Tutorials - Monitoring Attendance.mp4</t>
         </is>
       </c>
       <c r="L103" s="14" t="inlineStr">
@@ -18978,7 +18908,7 @@
       </c>
       <c r="T103" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U103" s="14" t="inlineStr">
@@ -18988,16 +18918,16 @@
       </c>
       <c r="V103" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W103" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
       <c r="A104" s="13" t="inlineStr">
         <is>
           <t>URL-103</t>
@@ -19046,7 +18976,7 @@
       <c r="J104" s="13" t="inlineStr"/>
       <c r="K104" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-102</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L104" s="13" t="inlineStr">
@@ -19057,11 +18987,7 @@
       <c r="M104" s="13" t="inlineStr"/>
       <c r="N104" s="13" t="inlineStr"/>
       <c r="O104" s="13" t="inlineStr"/>
-      <c r="P104" s="13" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P104" s="13" t="inlineStr"/>
       <c r="Q104" s="13" t="inlineStr"/>
       <c r="R104" s="13" t="inlineStr"/>
       <c r="S104" s="13" t="inlineStr">
@@ -19071,12 +18997,12 @@
       </c>
       <c r="T104" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U104" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V104" s="13" t="inlineStr">
@@ -19086,11 +19012,11 @@
       </c>
       <c r="W104" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
       <c r="A105" s="14" t="inlineStr">
         <is>
           <t>URL-104</t>
@@ -19139,7 +19065,7 @@
       <c r="J105" s="14" t="inlineStr"/>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>Source document: Day 3 Module 15.1 Observation and Charting.pdf</t>
+          <t>Day 3 Module 15.1 Observation and Charting.pdf</t>
         </is>
       </c>
       <c r="L105" s="14" t="inlineStr">
@@ -19159,12 +19085,16 @@
       </c>
       <c r="O105" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P105" s="14" t="inlineStr"/>
       <c r="Q105" s="14" t="inlineStr"/>
-      <c r="R105" s="14" t="inlineStr"/>
+      <c r="R105" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Day 3 Module 15.1 Observation and Charting.pdf</t>
+        </is>
+      </c>
       <c r="S105" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -19172,12 +19102,12 @@
       </c>
       <c r="T105" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U105" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V105" s="14" t="inlineStr">
@@ -19187,11 +19117,11 @@
       </c>
       <c r="W105" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
       <c r="A106" s="13" t="inlineStr">
         <is>
           <t>URL-105</t>
@@ -19240,7 +19170,7 @@
       <c r="J106" s="13" t="inlineStr"/>
       <c r="K106" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 23 - Measures and Records Manual Blood Pressure</t>
+          <t>CNA Skill 23 - Measures and Records Manual Blood Pressure</t>
         </is>
       </c>
       <c r="L106" s="13" t="inlineStr">
@@ -19265,7 +19195,7 @@
       </c>
       <c r="T106" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U106" s="13" t="inlineStr">
@@ -19275,16 +19205,16 @@
       </c>
       <c r="V106" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W106" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
       <c r="A107" s="14" t="inlineStr">
         <is>
           <t>URL-106</t>
@@ -19333,7 +19263,7 @@
       <c r="J107" s="14" t="inlineStr"/>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Submitting Assignments.mp4</t>
+          <t>Moodle Tutorials - Submitting Assignments.mp4</t>
         </is>
       </c>
       <c r="L107" s="14" t="inlineStr">
@@ -19358,7 +19288,7 @@
       </c>
       <c r="T107" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U107" s="14" t="inlineStr">
@@ -19368,16 +19298,16 @@
       </c>
       <c r="V107" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W107" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
       <c r="A108" s="13" t="inlineStr">
         <is>
           <t>URL-107</t>
@@ -19426,7 +19356,7 @@
       <c r="J108" s="13" t="inlineStr"/>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-106</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L108" s="13" t="inlineStr">
@@ -19437,11 +19367,7 @@
       <c r="M108" s="13" t="inlineStr"/>
       <c r="N108" s="13" t="inlineStr"/>
       <c r="O108" s="13" t="inlineStr"/>
-      <c r="P108" s="13" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P108" s="13" t="inlineStr"/>
       <c r="Q108" s="13" t="inlineStr"/>
       <c r="R108" s="13" t="inlineStr"/>
       <c r="S108" s="13" t="inlineStr">
@@ -19451,12 +19377,12 @@
       </c>
       <c r="T108" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U108" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V108" s="13" t="inlineStr">
@@ -19466,11 +19392,11 @@
       </c>
       <c r="W108" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
       <c r="A109" s="14" t="inlineStr">
         <is>
           <t>URL-108</t>
@@ -19519,7 +19445,7 @@
       <c r="J109" s="14" t="inlineStr"/>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 2 - Applies One Knee-High Elastic Stocking</t>
+          <t>CNA Skill 2 - Applies One Knee-High Elastic Stocking</t>
         </is>
       </c>
       <c r="L109" s="14" t="inlineStr">
@@ -19544,7 +19470,7 @@
       </c>
       <c r="T109" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U109" s="14" t="inlineStr">
@@ -19554,16 +19480,16 @@
       </c>
       <c r="V109" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W109" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
       <c r="A110" s="13" t="inlineStr">
         <is>
           <t>URL-109</t>
@@ -19612,7 +19538,7 @@
       <c r="J110" s="13" t="inlineStr"/>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-13.pdf</t>
         </is>
       </c>
       <c r="L110" s="13" t="inlineStr">
@@ -19632,12 +19558,16 @@
       </c>
       <c r="O110" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P110" s="13" t="inlineStr"/>
       <c r="Q110" s="13" t="inlineStr"/>
-      <c r="R110" s="13" t="inlineStr"/>
+      <c r="R110" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-13.pdf</t>
+        </is>
+      </c>
       <c r="S110" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -19645,12 +19575,12 @@
       </c>
       <c r="T110" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U110" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V110" s="13" t="inlineStr">
@@ -19660,11 +19590,11 @@
       </c>
       <c r="W110" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
       <c r="A111" s="14" t="inlineStr">
         <is>
           <t>URL-110</t>
@@ -19713,7 +19643,7 @@
       <c r="J111" s="14" t="inlineStr"/>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 15 - Performs Modified Passive Range of Motion (PROM) for One Knee and Ankle</t>
+          <t>CNA Skill 15 - Performs Modified Passive Range of Motion (PROM) for One Knee and Ankle</t>
         </is>
       </c>
       <c r="L111" s="14" t="inlineStr">
@@ -19738,7 +19668,7 @@
       </c>
       <c r="T111" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U111" s="14" t="inlineStr">
@@ -19748,16 +19678,16 @@
       </c>
       <c r="V111" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W111" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
       <c r="A112" s="13" t="inlineStr">
         <is>
           <t>URL-111</t>
@@ -19806,7 +19736,7 @@
       <c r="J112" s="13" t="inlineStr"/>
       <c r="K112" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 16 - Performs Modified Passive Range of Motion (PROM) for One Shoulder</t>
+          <t>CNA Skill 16 - Performs Modified Passive Range of Motion (PROM) for One Shoulder</t>
         </is>
       </c>
       <c r="L112" s="13" t="inlineStr">
@@ -19831,7 +19761,7 @@
       </c>
       <c r="T112" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U112" s="13" t="inlineStr">
@@ -19841,16 +19771,16 @@
       </c>
       <c r="V112" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W112" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
       <c r="A113" s="14" t="inlineStr">
         <is>
           <t>URL-112</t>
@@ -19899,7 +19829,7 @@
       <c r="J113" s="14" t="inlineStr"/>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-4.pdf</t>
         </is>
       </c>
       <c r="L113" s="14" t="inlineStr">
@@ -19919,12 +19849,16 @@
       </c>
       <c r="O113" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P113" s="14" t="inlineStr"/>
       <c r="Q113" s="14" t="inlineStr"/>
-      <c r="R113" s="14" t="inlineStr"/>
+      <c r="R113" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-4.pdf</t>
+        </is>
+      </c>
       <c r="S113" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -19932,12 +19866,12 @@
       </c>
       <c r="T113" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U113" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V113" s="14" t="inlineStr">
@@ -19947,11 +19881,11 @@
       </c>
       <c r="W113" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
       <c r="A114" s="13" t="inlineStr">
         <is>
           <t>URL-113</t>
@@ -20000,7 +19934,7 @@
       <c r="J114" s="13" t="inlineStr"/>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>Source document: PM Day 2 Module 2 Patient Resident Rights.pdf</t>
+          <t>PM Day 2 Module 2 Patient Resident Rights.pdf</t>
         </is>
       </c>
       <c r="L114" s="13" t="inlineStr">
@@ -20020,12 +19954,16 @@
       </c>
       <c r="O114" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P114" s="13" t="inlineStr"/>
       <c r="Q114" s="13" t="inlineStr"/>
-      <c r="R114" s="13" t="inlineStr"/>
+      <c r="R114" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 2 Module 2 Patient Resident Rights.pdf</t>
+        </is>
+      </c>
       <c r="S114" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -20033,12 +19971,12 @@
       </c>
       <c r="T114" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U114" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V114" s="13" t="inlineStr">
@@ -20048,11 +19986,11 @@
       </c>
       <c r="W114" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
       <c r="A115" s="14" t="inlineStr">
         <is>
           <t>URL-114</t>
@@ -20101,7 +20039,7 @@
       <c r="J115" s="14" t="inlineStr"/>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>Source document: Day 6 Module 15.2 Observation and Charting.pdf</t>
+          <t>Day 6 Module 15.2 Observation and Charting.pdf</t>
         </is>
       </c>
       <c r="L115" s="14" t="inlineStr">
@@ -20121,12 +20059,16 @@
       </c>
       <c r="O115" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P115" s="14" t="inlineStr"/>
       <c r="Q115" s="14" t="inlineStr"/>
-      <c r="R115" s="14" t="inlineStr"/>
+      <c r="R115" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Day 6 Module 15.2 Observation and Charting.pdf</t>
+        </is>
+      </c>
       <c r="S115" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -20134,12 +20076,12 @@
       </c>
       <c r="T115" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U115" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V115" s="14" t="inlineStr">
@@ -20149,11 +20091,11 @@
       </c>
       <c r="W115" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
       <c r="A116" s="13" t="inlineStr">
         <is>
           <t>URL-115</t>
@@ -20202,7 +20144,7 @@
       <c r="J116" s="13" t="inlineStr"/>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-6.pdf</t>
         </is>
       </c>
       <c r="L116" s="13" t="inlineStr">
@@ -20222,12 +20164,16 @@
       </c>
       <c r="O116" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P116" s="13" t="inlineStr"/>
       <c r="Q116" s="13" t="inlineStr"/>
-      <c r="R116" s="13" t="inlineStr"/>
+      <c r="R116" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-6.pdf</t>
+        </is>
+      </c>
       <c r="S116" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -20235,12 +20181,12 @@
       </c>
       <c r="T116" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U116" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V116" s="13" t="inlineStr">
@@ -20250,11 +20196,11 @@
       </c>
       <c r="W116" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
       <c r="A117" s="14" t="inlineStr">
         <is>
           <t>URL-116</t>
@@ -20303,7 +20249,7 @@
       <c r="J117" s="14" t="inlineStr"/>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-2.pdf</t>
         </is>
       </c>
       <c r="L117" s="14" t="inlineStr">
@@ -20323,12 +20269,16 @@
       </c>
       <c r="O117" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P117" s="14" t="inlineStr"/>
       <c r="Q117" s="14" t="inlineStr"/>
-      <c r="R117" s="14" t="inlineStr"/>
+      <c r="R117" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-2.pdf</t>
+        </is>
+      </c>
       <c r="S117" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -20336,12 +20286,12 @@
       </c>
       <c r="T117" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U117" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V117" s="14" t="inlineStr">
@@ -20351,11 +20301,11 @@
       </c>
       <c r="W117" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
       <c r="A118" s="13" t="inlineStr">
         <is>
           <t>URL-117</t>
@@ -20404,7 +20354,7 @@
       <c r="J118" s="13" t="inlineStr"/>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 20 - Provides Mouth Care</t>
+          <t>CNA Skill 20 - Provides Mouth Care</t>
         </is>
       </c>
       <c r="L118" s="13" t="inlineStr">
@@ -20429,7 +20379,7 @@
       </c>
       <c r="T118" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U118" s="13" t="inlineStr">
@@ -20439,16 +20389,16 @@
       </c>
       <c r="V118" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W118" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
       <c r="A119" s="14" t="inlineStr">
         <is>
           <t>URL-118</t>
@@ -20497,7 +20447,7 @@
       <c r="J119" s="14" t="inlineStr"/>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>Source document: Cover_Day_Text.png</t>
+          <t>Cover_Day_Text.png</t>
         </is>
       </c>
       <c r="L119" s="14" t="inlineStr">
@@ -20517,12 +20467,16 @@
       </c>
       <c r="O119" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P119" s="14" t="inlineStr"/>
       <c r="Q119" s="14" t="inlineStr"/>
-      <c r="R119" s="14" t="inlineStr"/>
+      <c r="R119" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Cover_Day_Text.png</t>
+        </is>
+      </c>
       <c r="S119" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -20530,12 +20484,12 @@
       </c>
       <c r="T119" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U119" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V119" s="14" t="inlineStr">
@@ -20545,11 +20499,11 @@
       </c>
       <c r="W119" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
       <c r="A120" s="13" t="inlineStr">
         <is>
           <t>URL-119</t>
@@ -20598,7 +20552,7 @@
       <c r="J120" s="13" t="inlineStr"/>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Accessing on Mobile.mp4</t>
+          <t>Moodle Tutorials - Accessing on Mobile.mp4</t>
         </is>
       </c>
       <c r="L120" s="13" t="inlineStr">
@@ -20623,7 +20577,7 @@
       </c>
       <c r="T120" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U120" s="13" t="inlineStr">
@@ -20633,16 +20587,16 @@
       </c>
       <c r="V120" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W120" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
       <c r="A121" s="14" t="inlineStr">
         <is>
           <t>URL-120</t>
@@ -20691,7 +20645,7 @@
       <c r="J121" s="14" t="inlineStr"/>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-119</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L121" s="14" t="inlineStr">
@@ -20702,11 +20656,7 @@
       <c r="M121" s="14" t="inlineStr"/>
       <c r="N121" s="14" t="inlineStr"/>
       <c r="O121" s="14" t="inlineStr"/>
-      <c r="P121" s="14" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P121" s="14" t="inlineStr"/>
       <c r="Q121" s="14" t="inlineStr"/>
       <c r="R121" s="14" t="inlineStr"/>
       <c r="S121" s="14" t="inlineStr">
@@ -20716,12 +20666,12 @@
       </c>
       <c r="T121" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U121" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V121" s="14" t="inlineStr">
@@ -20731,11 +20681,11 @@
       </c>
       <c r="W121" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
       <c r="A122" s="13" t="inlineStr">
         <is>
           <t>URL-121</t>
@@ -20784,7 +20734,7 @@
       <c r="J122" s="13" t="inlineStr"/>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Tracking Completion.mp4</t>
+          <t>Moodle Tutorials - Tracking Completion.mp4</t>
         </is>
       </c>
       <c r="L122" s="13" t="inlineStr">
@@ -20809,7 +20759,7 @@
       </c>
       <c r="T122" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U122" s="13" t="inlineStr">
@@ -20819,16 +20769,16 @@
       </c>
       <c r="V122" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W122" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
       <c r="A123" s="14" t="inlineStr">
         <is>
           <t>URL-122</t>
@@ -20877,7 +20827,7 @@
       <c r="J123" s="14" t="inlineStr"/>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-121</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L123" s="14" t="inlineStr">
@@ -20888,11 +20838,7 @@
       <c r="M123" s="14" t="inlineStr"/>
       <c r="N123" s="14" t="inlineStr"/>
       <c r="O123" s="14" t="inlineStr"/>
-      <c r="P123" s="14" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P123" s="14" t="inlineStr"/>
       <c r="Q123" s="14" t="inlineStr"/>
       <c r="R123" s="14" t="inlineStr"/>
       <c r="S123" s="14" t="inlineStr">
@@ -20902,12 +20848,12 @@
       </c>
       <c r="T123" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U123" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V123" s="14" t="inlineStr">
@@ -20917,11 +20863,11 @@
       </c>
       <c r="W123" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
       <c r="A124" s="13" t="inlineStr">
         <is>
           <t>URL-123</t>
@@ -20970,7 +20916,7 @@
       <c r="J124" s="13" t="inlineStr"/>
       <c r="K124" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-10.pdf</t>
         </is>
       </c>
       <c r="L124" s="13" t="inlineStr">
@@ -20990,12 +20936,16 @@
       </c>
       <c r="O124" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P124" s="13" t="inlineStr"/>
       <c r="Q124" s="13" t="inlineStr"/>
-      <c r="R124" s="13" t="inlineStr"/>
+      <c r="R124" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-10.pdf</t>
+        </is>
+      </c>
       <c r="S124" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -21003,12 +20953,12 @@
       </c>
       <c r="T124" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U124" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V124" s="13" t="inlineStr">
@@ -21018,11 +20968,11 @@
       </c>
       <c r="W124" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
       <c r="A125" s="14" t="inlineStr">
         <is>
           <t>URL-124</t>
@@ -21071,7 +21021,7 @@
       <c r="J125" s="14" t="inlineStr"/>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-5.pdf</t>
         </is>
       </c>
       <c r="L125" s="14" t="inlineStr">
@@ -21091,12 +21041,16 @@
       </c>
       <c r="O125" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P125" s="14" t="inlineStr"/>
       <c r="Q125" s="14" t="inlineStr"/>
-      <c r="R125" s="14" t="inlineStr"/>
+      <c r="R125" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-5.pdf</t>
+        </is>
+      </c>
       <c r="S125" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -21104,12 +21058,12 @@
       </c>
       <c r="T125" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U125" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V125" s="14" t="inlineStr">
@@ -21119,11 +21073,11 @@
       </c>
       <c r="W125" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
       <c r="A126" s="13" t="inlineStr">
         <is>
           <t>URL-125</t>
@@ -21172,7 +21126,7 @@
       <c r="J126" s="13" t="inlineStr"/>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CI-ION Meet Your Instructor and Coordinator_Revised.mp4</t>
+          <t>CI-ION Meet Your Instructor and Coordinator_Revised.mp4</t>
         </is>
       </c>
       <c r="L126" s="13" t="inlineStr">
@@ -21197,7 +21151,7 @@
       </c>
       <c r="T126" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U126" s="13" t="inlineStr">
@@ -21207,16 +21161,16 @@
       </c>
       <c r="V126" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W126" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
         <is>
           <t>URL-126</t>
@@ -21265,7 +21219,7 @@
       <c r="J127" s="14" t="inlineStr"/>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-14.pdf</t>
         </is>
       </c>
       <c r="L127" s="14" t="inlineStr">
@@ -21285,12 +21239,16 @@
       </c>
       <c r="O127" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P127" s="14" t="inlineStr"/>
       <c r="Q127" s="14" t="inlineStr"/>
-      <c r="R127" s="14" t="inlineStr"/>
+      <c r="R127" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-14.pdf</t>
+        </is>
+      </c>
       <c r="S127" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -21298,12 +21256,12 @@
       </c>
       <c r="T127" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U127" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V127" s="14" t="inlineStr">
@@ -21313,11 +21271,11 @@
       </c>
       <c r="W127" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
       <c r="A128" s="13" t="inlineStr">
         <is>
           <t>URL-127</t>
@@ -21366,7 +21324,7 @@
       <c r="J128" s="13" t="inlineStr"/>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>Source document: CI Institute of Nursing - Course Syllabus.pdf</t>
+          <t>CI Institute of Nursing - Course Syllabus.pdf</t>
         </is>
       </c>
       <c r="L128" s="13" t="inlineStr">
@@ -21386,12 +21344,16 @@
       </c>
       <c r="O128" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P128" s="13" t="inlineStr"/>
       <c r="Q128" s="13" t="inlineStr"/>
-      <c r="R128" s="13" t="inlineStr"/>
+      <c r="R128" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\CI Institute of Nursing - Course Syllabus.pdf</t>
+        </is>
+      </c>
       <c r="S128" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -21399,12 +21361,12 @@
       </c>
       <c r="T128" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U128" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V128" s="13" t="inlineStr">
@@ -21414,11 +21376,11 @@
       </c>
       <c r="W128" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
       <c r="A129" s="14" t="inlineStr">
         <is>
           <t>URL-128</t>
@@ -21467,7 +21429,7 @@
       <c r="J129" s="14" t="inlineStr"/>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 1 Module 2 Patient Resident Rights.pdf</t>
+          <t>PM Day 1 Module 2 Patient Resident Rights.pdf</t>
         </is>
       </c>
       <c r="L129" s="14" t="inlineStr">
@@ -21487,12 +21449,16 @@
       </c>
       <c r="O129" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P129" s="14" t="inlineStr"/>
       <c r="Q129" s="14" t="inlineStr"/>
-      <c r="R129" s="14" t="inlineStr"/>
+      <c r="R129" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 1 Module 2 Patient Resident Rights.pdf</t>
+        </is>
+      </c>
       <c r="S129" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -21500,12 +21466,12 @@
       </c>
       <c r="T129" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U129" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V129" s="14" t="inlineStr">
@@ -21515,11 +21481,11 @@
       </c>
       <c r="W129" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
       <c r="A130" s="13" t="inlineStr">
         <is>
           <t>URL-129</t>
@@ -21568,7 +21534,7 @@
       <c r="J130" s="13" t="inlineStr"/>
       <c r="K130" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-15.pdf</t>
         </is>
       </c>
       <c r="L130" s="13" t="inlineStr">
@@ -21588,12 +21554,16 @@
       </c>
       <c r="O130" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P130" s="13" t="inlineStr"/>
       <c r="Q130" s="13" t="inlineStr"/>
-      <c r="R130" s="13" t="inlineStr"/>
+      <c r="R130" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-15.pdf</t>
+        </is>
+      </c>
       <c r="S130" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -21601,12 +21571,12 @@
       </c>
       <c r="T130" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U130" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V130" s="13" t="inlineStr">
@@ -21616,11 +21586,11 @@
       </c>
       <c r="W130" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
       <c r="A131" s="14" t="inlineStr">
         <is>
           <t>URL-130</t>
@@ -21669,7 +21639,7 @@
       <c r="J131" s="14" t="inlineStr"/>
       <c r="K131" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-9.pdf</t>
         </is>
       </c>
       <c r="L131" s="14" t="inlineStr">
@@ -21689,12 +21659,16 @@
       </c>
       <c r="O131" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P131" s="14" t="inlineStr"/>
       <c r="Q131" s="14" t="inlineStr"/>
-      <c r="R131" s="14" t="inlineStr"/>
+      <c r="R131" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-9.pdf</t>
+        </is>
+      </c>
       <c r="S131" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -21702,12 +21676,12 @@
       </c>
       <c r="T131" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U131" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V131" s="14" t="inlineStr">
@@ -21717,11 +21691,11 @@
       </c>
       <c r="W131" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
       <c r="A132" s="13" t="inlineStr">
         <is>
           <t>URL-131</t>
@@ -21770,7 +21744,7 @@
       <c r="J132" s="13" t="inlineStr"/>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 21 - Provides for Perineal Care for Female</t>
+          <t>CNA Skill 21 - Provides for Perineal Care for Female</t>
         </is>
       </c>
       <c r="L132" s="13" t="inlineStr">
@@ -21795,7 +21769,7 @@
       </c>
       <c r="T132" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U132" s="13" t="inlineStr">
@@ -21805,16 +21779,16 @@
       </c>
       <c r="V132" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W132" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
       <c r="A133" s="14" t="inlineStr">
         <is>
           <t>URL-132</t>
@@ -21863,7 +21837,7 @@
       <c r="J133" s="14" t="inlineStr"/>
       <c r="K133" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 13 Module 9 Patient Care Procedures-1-31.pdf</t>
+          <t>PM Day 13 Module 9 Patient Care Procedures-1-31.pdf</t>
         </is>
       </c>
       <c r="L133" s="14" t="inlineStr">
@@ -21883,12 +21857,16 @@
       </c>
       <c r="O133" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P133" s="14" t="inlineStr"/>
       <c r="Q133" s="14" t="inlineStr"/>
-      <c r="R133" s="14" t="inlineStr"/>
+      <c r="R133" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 13 Module 9 Patient Care Procedures-1-31.pdf</t>
+        </is>
+      </c>
       <c r="S133" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -21896,12 +21874,12 @@
       </c>
       <c r="T133" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U133" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V133" s="14" t="inlineStr">
@@ -21911,11 +21889,11 @@
       </c>
       <c r="W133" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
       <c r="A134" s="13" t="inlineStr">
         <is>
           <t>URL-133</t>
@@ -21964,7 +21942,7 @@
       <c r="J134" s="13" t="inlineStr"/>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>Source document: PM Day 14 Module 9 Patient Care Procedures-32-43.pdf</t>
+          <t>PM Day 14 Module 9 Patient Care Procedures-32-43.pdf</t>
         </is>
       </c>
       <c r="L134" s="13" t="inlineStr">
@@ -21984,12 +21962,16 @@
       </c>
       <c r="O134" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P134" s="13" t="inlineStr"/>
       <c r="Q134" s="13" t="inlineStr"/>
-      <c r="R134" s="13" t="inlineStr"/>
+      <c r="R134" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 14 Module 9 Patient Care Procedures-32-43.pdf</t>
+        </is>
+      </c>
       <c r="S134" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -21997,12 +21979,12 @@
       </c>
       <c r="T134" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U134" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V134" s="13" t="inlineStr">
@@ -22012,11 +21994,11 @@
       </c>
       <c r="W134" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
       <c r="A135" s="14" t="inlineStr">
         <is>
           <t>URL-134</t>
@@ -22065,7 +22047,7 @@
       <c r="J135" s="14" t="inlineStr"/>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Viewing Grades.mp4</t>
+          <t>Moodle Tutorials - Viewing Grades.mp4</t>
         </is>
       </c>
       <c r="L135" s="14" t="inlineStr">
@@ -22090,7 +22072,7 @@
       </c>
       <c r="T135" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U135" s="14" t="inlineStr">
@@ -22100,16 +22082,16 @@
       </c>
       <c r="V135" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W135" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
       <c r="A136" s="13" t="inlineStr">
         <is>
           <t>URL-135</t>
@@ -22158,7 +22140,7 @@
       <c r="J136" s="13" t="inlineStr"/>
       <c r="K136" s="13" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-134</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L136" s="13" t="inlineStr">
@@ -22169,11 +22151,7 @@
       <c r="M136" s="13" t="inlineStr"/>
       <c r="N136" s="13" t="inlineStr"/>
       <c r="O136" s="13" t="inlineStr"/>
-      <c r="P136" s="13" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P136" s="13" t="inlineStr"/>
       <c r="Q136" s="13" t="inlineStr"/>
       <c r="R136" s="13" t="inlineStr"/>
       <c r="S136" s="13" t="inlineStr">
@@ -22183,12 +22161,12 @@
       </c>
       <c r="T136" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U136" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V136" s="13" t="inlineStr">
@@ -22198,11 +22176,11 @@
       </c>
       <c r="W136" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
       <c r="A137" s="14" t="inlineStr">
         <is>
           <t>URL-136</t>
@@ -22251,7 +22229,7 @@
       <c r="J137" s="14" t="inlineStr"/>
       <c r="K137" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 3 - Assist to Ambulate Using Transfer Belt</t>
+          <t>CNA Skill 3 - Assist to Ambulate Using Transfer Belt</t>
         </is>
       </c>
       <c r="L137" s="14" t="inlineStr">
@@ -22276,7 +22254,7 @@
       </c>
       <c r="T137" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U137" s="14" t="inlineStr">
@@ -22286,16 +22264,16 @@
       </c>
       <c r="V137" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W137" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
       <c r="A138" s="13" t="inlineStr">
         <is>
           <t>URL-137</t>
@@ -22344,7 +22322,7 @@
       <c r="J138" s="13" t="inlineStr"/>
       <c r="K138" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: Moodle Tutorials - Using Privating Messaging.mp4</t>
+          <t>Moodle Tutorials - Using Privating Messaging.mp4</t>
         </is>
       </c>
       <c r="L138" s="13" t="inlineStr">
@@ -22369,7 +22347,7 @@
       </c>
       <c r="T138" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U138" s="13" t="inlineStr">
@@ -22379,16 +22357,16 @@
       </c>
       <c r="V138" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W138" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
       <c r="A139" s="14" t="inlineStr">
         <is>
           <t>URL-138</t>
@@ -22437,7 +22415,7 @@
       <c r="J139" s="14" t="inlineStr"/>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>Duplicate / alternate anchor of URL-137</t>
+          <t>Duplicate/alternate tab anchor of canonical source item</t>
         </is>
       </c>
       <c r="L139" s="14" t="inlineStr">
@@ -22448,11 +22426,7 @@
       <c r="M139" s="14" t="inlineStr"/>
       <c r="N139" s="14" t="inlineStr"/>
       <c r="O139" s="14" t="inlineStr"/>
-      <c r="P139" s="14" t="inlineStr">
-        <is>
-          <t>Video files are skipped to avoid Apps Script ZIP size failures.</t>
-        </is>
-      </c>
+      <c r="P139" s="14" t="inlineStr"/>
       <c r="Q139" s="14" t="inlineStr"/>
       <c r="R139" s="14" t="inlineStr"/>
       <c r="S139" s="14" t="inlineStr">
@@ -22462,12 +22436,12 @@
       </c>
       <c r="T139" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U139" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V139" s="14" t="inlineStr">
@@ -22477,11 +22451,11 @@
       </c>
       <c r="W139" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
       <c r="A140" s="13" t="inlineStr">
         <is>
           <t>URL-139</t>
@@ -22530,7 +22504,7 @@
       <c r="J140" s="13" t="inlineStr"/>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 12 - Measures and Records Electronic Blood Pressure</t>
+          <t>CNA Skill 12 - Measures and Records Electronic Blood Pressure</t>
         </is>
       </c>
       <c r="L140" s="13" t="inlineStr">
@@ -22555,7 +22529,7 @@
       </c>
       <c r="T140" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U140" s="13" t="inlineStr">
@@ -22565,16 +22539,16 @@
       </c>
       <c r="V140" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W140" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
       <c r="A141" s="14" t="inlineStr">
         <is>
           <t>URL-140</t>
@@ -22623,7 +22597,7 @@
       <c r="J141" s="14" t="inlineStr"/>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 8 Module 8 Patient Care Skills-12-16.pdf</t>
+          <t>PM Day 8 Module 8 Patient Care Skills-12-16.pdf</t>
         </is>
       </c>
       <c r="L141" s="14" t="inlineStr">
@@ -22643,12 +22617,16 @@
       </c>
       <c r="O141" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P141" s="14" t="inlineStr"/>
       <c r="Q141" s="14" t="inlineStr"/>
-      <c r="R141" s="14" t="inlineStr"/>
+      <c r="R141" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 8 Module 8 Patient Care Skills-12-16.pdf</t>
+        </is>
+      </c>
       <c r="S141" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -22656,12 +22634,12 @@
       </c>
       <c r="T141" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U141" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V141" s="14" t="inlineStr">
@@ -22671,11 +22649,11 @@
       </c>
       <c r="W141" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
       <c r="A142" s="13" t="inlineStr">
         <is>
           <t>URL-141</t>
@@ -22724,7 +22702,7 @@
       <c r="J142" s="13" t="inlineStr"/>
       <c r="K142" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 7 - Counts and Records Respirations</t>
+          <t>CNA Skill 7 - Counts and Records Respirations</t>
         </is>
       </c>
       <c r="L142" s="13" t="inlineStr">
@@ -22749,7 +22727,7 @@
       </c>
       <c r="T142" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U142" s="13" t="inlineStr">
@@ -22759,16 +22737,16 @@
       </c>
       <c r="V142" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W142" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
       <c r="A143" s="14" t="inlineStr">
         <is>
           <t>URL-142</t>
@@ -22817,7 +22795,7 @@
       <c r="J143" s="14" t="inlineStr"/>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-7.pdf</t>
         </is>
       </c>
       <c r="L143" s="14" t="inlineStr">
@@ -22837,12 +22815,16 @@
       </c>
       <c r="O143" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P143" s="14" t="inlineStr"/>
       <c r="Q143" s="14" t="inlineStr"/>
-      <c r="R143" s="14" t="inlineStr"/>
+      <c r="R143" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-7.pdf</t>
+        </is>
+      </c>
       <c r="S143" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -22850,12 +22832,12 @@
       </c>
       <c r="T143" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U143" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V143" s="14" t="inlineStr">
@@ -22865,11 +22847,11 @@
       </c>
       <c r="W143" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
       <c r="A144" s="13" t="inlineStr">
         <is>
           <t>URL-143</t>
@@ -22918,7 +22900,7 @@
       <c r="J144" s="13" t="inlineStr"/>
       <c r="K144" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-11.pdf</t>
         </is>
       </c>
       <c r="L144" s="13" t="inlineStr">
@@ -22938,12 +22920,16 @@
       </c>
       <c r="O144" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P144" s="13" t="inlineStr"/>
       <c r="Q144" s="13" t="inlineStr"/>
-      <c r="R144" s="13" t="inlineStr"/>
+      <c r="R144" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-11.pdf</t>
+        </is>
+      </c>
       <c r="S144" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -22951,12 +22937,12 @@
       </c>
       <c r="T144" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U144" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V144" s="13" t="inlineStr">
@@ -22966,11 +22952,11 @@
       </c>
       <c r="W144" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
       <c r="A145" s="14" t="inlineStr">
         <is>
           <t>URL-144</t>
@@ -23019,7 +23005,7 @@
       <c r="J145" s="14" t="inlineStr"/>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 10 Module 8 Patient Care Skills-11-23.pdf</t>
+          <t>PM Day 10 Module 8 Patient Care Skills-11-23.pdf</t>
         </is>
       </c>
       <c r="L145" s="14" t="inlineStr">
@@ -23039,12 +23025,16 @@
       </c>
       <c r="O145" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P145" s="14" t="inlineStr"/>
       <c r="Q145" s="14" t="inlineStr"/>
-      <c r="R145" s="14" t="inlineStr"/>
+      <c r="R145" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 10 Module 8 Patient Care Skills-11-23.pdf</t>
+        </is>
+      </c>
       <c r="S145" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -23052,12 +23042,12 @@
       </c>
       <c r="T145" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U145" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V145" s="14" t="inlineStr">
@@ -23067,11 +23057,11 @@
       </c>
       <c r="W145" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
       <c r="A146" s="13" t="inlineStr">
         <is>
           <t>URL-145</t>
@@ -23120,7 +23110,7 @@
       <c r="J146" s="13" t="inlineStr"/>
       <c r="K146" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-17.pdf</t>
         </is>
       </c>
       <c r="L146" s="13" t="inlineStr">
@@ -23140,12 +23130,16 @@
       </c>
       <c r="O146" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P146" s="13" t="inlineStr"/>
       <c r="Q146" s="13" t="inlineStr"/>
-      <c r="R146" s="13" t="inlineStr"/>
+      <c r="R146" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-17.pdf</t>
+        </is>
+      </c>
       <c r="S146" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -23153,12 +23147,12 @@
       </c>
       <c r="T146" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U146" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V146" s="13" t="inlineStr">
@@ -23168,11 +23162,11 @@
       </c>
       <c r="W146" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
       <c r="A147" s="14" t="inlineStr">
         <is>
           <t>URL-146</t>
@@ -23221,7 +23215,7 @@
       <c r="J147" s="14" t="inlineStr"/>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 7 Module 8 Patient Care Skills-1-11.pdf</t>
+          <t>PM Day 7 Module 8 Patient Care Skills-1-11.pdf</t>
         </is>
       </c>
       <c r="L147" s="14" t="inlineStr">
@@ -23241,12 +23235,16 @@
       </c>
       <c r="O147" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P147" s="14" t="inlineStr"/>
       <c r="Q147" s="14" t="inlineStr"/>
-      <c r="R147" s="14" t="inlineStr"/>
+      <c r="R147" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 7 Module 8 Patient Care Skills-1-11.pdf</t>
+        </is>
+      </c>
       <c r="S147" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -23254,12 +23252,12 @@
       </c>
       <c r="T147" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U147" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V147" s="14" t="inlineStr">
@@ -23269,11 +23267,11 @@
       </c>
       <c r="W147" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
       <c r="A148" s="13" t="inlineStr">
         <is>
           <t>URL-147</t>
@@ -23322,7 +23320,7 @@
       <c r="J148" s="13" t="inlineStr"/>
       <c r="K148" s="13" t="inlineStr">
         <is>
-          <t>Source document: AM Day 6 / PM Day 11 Module 8 Patient Care Skills.pdf</t>
+          <t>AM Day 6 / PM Day 11 Module 8 Patient Care Skills.pdf</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr">
@@ -23342,12 +23340,16 @@
       </c>
       <c r="O148" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P148" s="13" t="inlineStr"/>
       <c r="Q148" s="13" t="inlineStr"/>
-      <c r="R148" s="13" t="inlineStr"/>
+      <c r="R148" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\AM Day 6 - PM Day 11 Module 8 Patient Care Skills.pdf</t>
+        </is>
+      </c>
       <c r="S148" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -23355,12 +23357,12 @@
       </c>
       <c r="T148" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U148" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V148" s="13" t="inlineStr">
@@ -23370,11 +23372,11 @@
       </c>
       <c r="W148" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
       <c r="A149" s="14" t="inlineStr">
         <is>
           <t>URL-148</t>
@@ -23423,7 +23425,7 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="14" t="inlineStr">
         <is>
-          <t>Source document: CI-ION NATP Final Exam.pdf</t>
+          <t>CI-ION NATP Final Exam.pdf</t>
         </is>
       </c>
       <c r="L149" s="14" t="inlineStr">
@@ -23443,12 +23445,16 @@
       </c>
       <c r="O149" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P149" s="14" t="inlineStr"/>
       <c r="Q149" s="14" t="inlineStr"/>
-      <c r="R149" s="14" t="inlineStr"/>
+      <c r="R149" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\CI-ION NATP Final Exam.pdf</t>
+        </is>
+      </c>
       <c r="S149" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -23456,12 +23462,12 @@
       </c>
       <c r="T149" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U149" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V149" s="14" t="inlineStr">
@@ -23471,11 +23477,11 @@
       </c>
       <c r="W149" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
       <c r="A150" s="13" t="inlineStr">
         <is>
           <t>URL-149</t>
@@ -23524,7 +23530,7 @@
       <c r="J150" s="13" t="inlineStr"/>
       <c r="K150" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 14 - Measures and Records Weight of Ambulatory Client</t>
+          <t>CNA Skill 14 - Measures and Records Weight of Ambulatory Client</t>
         </is>
       </c>
       <c r="L150" s="13" t="inlineStr">
@@ -23549,7 +23555,7 @@
       </c>
       <c r="T150" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U150" s="13" t="inlineStr">
@@ -23559,16 +23565,16 @@
       </c>
       <c r="V150" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W150" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
       <c r="A151" s="14" t="inlineStr">
         <is>
           <t>URL-150</t>
@@ -23617,7 +23623,7 @@
       <c r="J151" s="14" t="inlineStr"/>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 5 - Cleans Upper or Lower Denture</t>
+          <t>CNA Skill 5 - Cleans Upper or Lower Denture</t>
         </is>
       </c>
       <c r="L151" s="14" t="inlineStr">
@@ -23642,7 +23648,7 @@
       </c>
       <c r="T151" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U151" s="14" t="inlineStr">
@@ -23652,16 +23658,16 @@
       </c>
       <c r="V151" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W151" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
       <c r="A152" s="13" t="inlineStr">
         <is>
           <t>URL-151</t>
@@ -23710,7 +23716,7 @@
       <c r="J152" s="13" t="inlineStr"/>
       <c r="K152" s="13" t="inlineStr">
         <is>
-          <t>CCCCO NA model curriculum source module</t>
+          <t>cccco-na-model-curriculum-module-8.pdf</t>
         </is>
       </c>
       <c r="L152" s="13" t="inlineStr">
@@ -23730,12 +23736,16 @@
       </c>
       <c r="O152" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P152" s="13" t="inlineStr"/>
       <c r="Q152" s="13" t="inlineStr"/>
-      <c r="R152" s="13" t="inlineStr"/>
+      <c r="R152" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\cccco-na-model-curriculum-module-8.pdf</t>
+        </is>
+      </c>
       <c r="S152" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -23743,12 +23753,12 @@
       </c>
       <c r="T152" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U152" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V152" s="13" t="inlineStr">
@@ -23758,11 +23768,11 @@
       </c>
       <c r="W152" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
       <c r="A153" s="14" t="inlineStr">
         <is>
           <t>URL-152</t>
@@ -23811,7 +23821,7 @@
       <c r="J153" s="14" t="inlineStr"/>
       <c r="K153" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 16 Module 13 Long Term Patient Resident.pdf</t>
+          <t>PM Day 16 Module 13 Long Term Patient Resident.pdf</t>
         </is>
       </c>
       <c r="L153" s="14" t="inlineStr">
@@ -23831,12 +23841,16 @@
       </c>
       <c r="O153" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P153" s="14" t="inlineStr"/>
       <c r="Q153" s="14" t="inlineStr"/>
-      <c r="R153" s="14" t="inlineStr"/>
+      <c r="R153" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 16 Module 13 Long Term Patient Resident.pdf</t>
+        </is>
+      </c>
       <c r="S153" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -23844,12 +23858,12 @@
       </c>
       <c r="T153" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U153" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V153" s="14" t="inlineStr">
@@ -23859,11 +23873,11 @@
       </c>
       <c r="W153" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
       <c r="A154" s="13" t="inlineStr">
         <is>
           <t>URL-153</t>
@@ -23912,7 +23926,7 @@
       <c r="J154" s="13" t="inlineStr"/>
       <c r="K154" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 13 - Measures and Records Urinary Output</t>
+          <t>CNA Skill 13 - Measures and Records Urinary Output</t>
         </is>
       </c>
       <c r="L154" s="13" t="inlineStr">
@@ -23937,7 +23951,7 @@
       </c>
       <c r="T154" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U154" s="13" t="inlineStr">
@@ -23947,16 +23961,16 @@
       </c>
       <c r="V154" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W154" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
       <c r="A155" s="14" t="inlineStr">
         <is>
           <t>URL-154</t>
@@ -24005,7 +24019,7 @@
       <c r="J155" s="14" t="inlineStr"/>
       <c r="K155" s="14" t="inlineStr">
         <is>
-          <t>Source document: Request for Live Scan Service (Example)  .pdf</t>
+          <t>Request for Live Scan Service (Example)  .pdf</t>
         </is>
       </c>
       <c r="L155" s="14" t="inlineStr">
@@ -24025,12 +24039,16 @@
       </c>
       <c r="O155" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P155" s="14" t="inlineStr"/>
       <c r="Q155" s="14" t="inlineStr"/>
-      <c r="R155" s="14" t="inlineStr"/>
+      <c r="R155" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Request for Live Scan Service (Example) .pdf</t>
+        </is>
+      </c>
       <c r="S155" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -24038,12 +24056,12 @@
       </c>
       <c r="T155" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U155" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V155" s="14" t="inlineStr">
@@ -24053,11 +24071,11 @@
       </c>
       <c r="W155" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
       <c r="A156" s="13" t="inlineStr">
         <is>
           <t>URL-155</t>
@@ -24106,7 +24124,7 @@
       <c r="J156" s="13" t="inlineStr"/>
       <c r="K156" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 22 - Transfers from Bed to Wheelchair Using Transfer Belt</t>
+          <t>CNA Skill 22 - Transfers from Bed to Wheelchair Using Transfer Belt</t>
         </is>
       </c>
       <c r="L156" s="13" t="inlineStr">
@@ -24131,7 +24149,7 @@
       </c>
       <c r="T156" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U156" s="13" t="inlineStr">
@@ -24141,16 +24159,16 @@
       </c>
       <c r="V156" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W156" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
       <c r="A157" s="14" t="inlineStr">
         <is>
           <t>URL-156</t>
@@ -24199,7 +24217,7 @@
       <c r="J157" s="14" t="inlineStr"/>
       <c r="K157" s="14" t="inlineStr">
         <is>
-          <t>Source document: PM Day 9 Module 8 Patient Care Skills-1-10.pdf</t>
+          <t>PM Day 9 Module 8 Patient Care Skills-1-10.pdf</t>
         </is>
       </c>
       <c r="L157" s="14" t="inlineStr">
@@ -24219,12 +24237,16 @@
       </c>
       <c r="O157" s="14" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P157" s="14" t="inlineStr"/>
       <c r="Q157" s="14" t="inlineStr"/>
-      <c r="R157" s="14" t="inlineStr"/>
+      <c r="R157" s="14" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\PM Day 9 Module 8 Patient Care Skills-1-10.pdf</t>
+        </is>
+      </c>
       <c r="S157" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -24232,12 +24254,12 @@
       </c>
       <c r="T157" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U157" s="14" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V157" s="14" t="inlineStr">
@@ -24247,11 +24269,11 @@
       </c>
       <c r="W157" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
       <c r="A158" s="13" t="inlineStr">
         <is>
           <t>URL-157</t>
@@ -24300,7 +24322,7 @@
       <c r="J158" s="13" t="inlineStr"/>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>Source document: Cover_Night_Text.png</t>
+          <t>Cover_Night_Text.png</t>
         </is>
       </c>
       <c r="L158" s="13" t="inlineStr">
@@ -24320,12 +24342,16 @@
       </c>
       <c r="O158" s="13" t="inlineStr">
         <is>
-          <t>linked-files/</t>
+          <t>linked-files</t>
         </is>
       </c>
       <c r="P158" s="13" t="inlineStr"/>
       <c r="Q158" s="13" t="inlineStr"/>
-      <c r="R158" s="13" t="inlineStr"/>
+      <c r="R158" s="13" t="inlineStr">
+        <is>
+          <t>CNA-Recert-Course\CI-ION-course-export-CI-ION - Course Structures - Contents-20260601-114428\linked-files\Cover_Night_Text.png</t>
+        </is>
+      </c>
       <c r="S158" s="13" t="inlineStr">
         <is>
           <t>No</t>
@@ -24333,12 +24359,12 @@
       </c>
       <c r="T158" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U158" s="13" t="inlineStr">
         <is>
-          <t>Program Owner</t>
+          <t>Repo Auditor</t>
         </is>
       </c>
       <c r="V158" s="13" t="inlineStr">
@@ -24348,11 +24374,11 @@
       </c>
       <c r="W158" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
       <c r="A159" s="14" t="inlineStr">
         <is>
           <t>URL-158</t>
@@ -24401,7 +24427,7 @@
       <c r="J159" s="14" t="inlineStr"/>
       <c r="K159" s="14" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 10 - Feeds Client Who Cannot Feed Self</t>
+          <t>CNA Skill 10 - Feeds Client Who Cannot Feed Self</t>
         </is>
       </c>
       <c r="L159" s="14" t="inlineStr">
@@ -24426,7 +24452,7 @@
       </c>
       <c r="T159" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U159" s="14" t="inlineStr">
@@ -24436,16 +24462,16 @@
       </c>
       <c r="V159" s="14" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W159" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
       <c r="A160" s="13" t="inlineStr">
         <is>
           <t>URL-159</t>
@@ -24494,7 +24520,7 @@
       <c r="J160" s="13" t="inlineStr"/>
       <c r="K160" s="13" t="inlineStr">
         <is>
-          <t>Skipped media/large file: CNA Skill 4 - Bedpan</t>
+          <t>CNA Skill 4 - Bedpan</t>
         </is>
       </c>
       <c r="L160" s="13" t="inlineStr">
@@ -24519,7 +24545,7 @@
       </c>
       <c r="T160" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U160" s="13" t="inlineStr">
@@ -24529,16 +24555,16 @@
       </c>
       <c r="V160" s="13" t="inlineStr">
         <is>
-          <t>P2 High</t>
+          <t>P2 Medium</t>
         </is>
       </c>
       <c r="W160" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=drive.google.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
       <c r="A161" s="14" t="inlineStr">
         <is>
           <t>URL-160</t>
@@ -24583,7 +24609,7 @@
       <c r="J161" s="14" t="inlineStr"/>
       <c r="K161" s="14" t="inlineStr">
         <is>
-          <t>Live Moodle course shell (id=13)</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L161" s="14" t="inlineStr">
@@ -24604,7 +24630,7 @@
       </c>
       <c r="T161" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U161" s="14" t="inlineStr">
@@ -24619,11 +24645,11 @@
       </c>
       <c r="W161" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=learn.ciinstituteofnursing.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
       <c r="A162" s="13" t="inlineStr">
         <is>
           <t>URL-161</t>
@@ -24668,7 +24694,7 @@
       <c r="J162" s="13" t="inlineStr"/>
       <c r="K162" s="13" t="inlineStr">
         <is>
-          <t>Facility/location map reference</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L162" s="13" t="inlineStr">
@@ -24689,7 +24715,7 @@
       </c>
       <c r="T162" s="13" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U162" s="13" t="inlineStr">
@@ -24704,11 +24730,11 @@
       </c>
       <c r="W162" s="13" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=maps.app.goo.gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="30" customHeight="1">
+          <t>Recalculated from manifest.json on 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
       <c r="A163" s="14" t="inlineStr">
         <is>
           <t>URL-162</t>
@@ -24753,7 +24779,7 @@
       <c r="J163" s="14" t="inlineStr"/>
       <c r="K163" s="14" t="inlineStr">
         <is>
-          <t>CI-ION user-flow design board</t>
+          <t>External web reference; not local evidence unless separately documented</t>
         </is>
       </c>
       <c r="L163" s="14" t="inlineStr">
@@ -24774,7 +24800,7 @@
       </c>
       <c r="T163" s="14" t="inlineStr">
         <is>
-          <t>See Copy Status / Master Tracker</t>
+          <t>Re-export/import/owner decision if not copied; parse xlsx position</t>
         </is>
       </c>
       <c r="U163" s="14" t="inlineStr">
@@ -24789,7 +24815,7 @@
       </c>
       <c r="W163" s="14" t="inlineStr">
         <is>
-          <t>From manifest.json links_found; host=www.figma.com</t>
+          <t>Recalculated from manifest.json on 2026-06-03</t>
         </is>
       </c>
     </row>
@@ -25026,42 +25052,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Item / Pattern</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Size (bytes)</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>Copy Status</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
@@ -25758,42 +25784,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Documentation Area</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Target File / Location</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>Owner Role</t>
         </is>
@@ -26286,32 +26312,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Target Minutes</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Repo Source File</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Export Source Evidence</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -26557,19 +26583,30 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+    </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>TOTAL REQUIRED THEORY (target)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="31" t="n">
         <v>720</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="32">
         <f> 720 min / 12.0 h</f>
         <v/>
       </c>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F9"/>
@@ -26630,32 +26667,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Assessment Item</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Repo Source</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Export/App Evidence</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -26880,32 +26917,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Gate Control</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Control Doc</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>App/Export Evidence</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -27246,32 +27283,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Separation Control</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Control Doc</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>App/Export Evidence</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
